--- a/Карнаухова Ольга Александровна/Математический анализ (Часть 2)/Журнал событий (id 1182).xlsx
+++ b/Карнаухова Ольга Александровна/Математический анализ (Часть 2)/Журнал событий (id 1182).xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:I187"/>
   <sheetData>
     <row r="1" spans="1:9" customHeight="0">
       <c r="A1" s="0" t="inlineStr">
@@ -112,7 +112,7 @@
     <row r="2" spans="1:9" customHeight="0">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:29:56</t>
+          <t>13/10/26, 13:28:29</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -159,17 +159,17 @@
     <row r="3" spans="1:9" customHeight="0">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:18:39</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -179,44 +179,39 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' unenrolled the user with id '208503' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I3" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:9" customHeight="0">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:18:37</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -226,44 +221,39 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653269' for the user with id '208503' for the grade item with id '712649'.</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:9" customHeight="0">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>9/10/26, 20:27:09</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Сансызбай Нурбакыт -</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -278,29 +268,24 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222555' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653249' for the user with id '208503' for the grade item with id '666279'.</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="inlineStr">
-        <is>
-          <t>91.79.229.252</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:9" customHeight="0">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>7/10/26, 05:48:36</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -310,7 +295,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -325,39 +310,34 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Просмотрено описание курса</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653268' for the user with id '208503' for the grade item with id '524410'.</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I6" s="0" t="inlineStr">
-        <is>
-          <t>87.250.224.238</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:9" customHeight="0">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:19</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -367,44 +347,39 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653267' for the user with id '208503' for the grade item with id '212337'.</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:9" customHeight="0">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:14</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -414,44 +389,39 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653251' for the user with id '208503' for the grade item with id '202565'.</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:9" customHeight="0">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:07</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -466,29 +436,24 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653250' for the user with id '208503' for the grade item with id '202489'.</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:9" customHeight="0">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>3/10/26, 05:43:06</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
@@ -498,7 +463,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Волков Даниил Феликсович</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -513,12 +478,12 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '207098'.</t>
+          <t>The user with id '0' deleted the grade with id '61653266' for the user with id '208503' for the grade item with id '193468'.</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -530,7 +495,7 @@
     <row r="11" spans="1:9" customHeight="0">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>3/10/26, 05:43:06</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
@@ -540,7 +505,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Волков Даниил Феликсович</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -555,12 +520,12 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '207098' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653265' for the user with id '208503' for the grade item with id '162883'.</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -572,17 +537,17 @@
     <row r="12" spans="1:9" customHeight="0">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:16</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -592,44 +557,39 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653264' for the user with id '208503' for the grade item with id '162882'.</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:9" customHeight="0">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:12</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -639,44 +599,39 @@
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653248' for the user with id '208503' for the grade item with id '162872'.</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:9" customHeight="0">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:04</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -691,39 +646,34 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653263' for the user with id '208503' for the grade item with id '13852'.</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:9" customHeight="0">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 09:51:46</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -738,39 +688,34 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653262' for the user with id '208503' for the grade item with id '13850'.</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:9" customHeight="0">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:31</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -780,44 +725,39 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653261' for the user with id '208503' for the grade item with id '13847'.</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:9" customHeight="0">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:26</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -827,44 +767,39 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653260' for the user with id '208503' for the grade item with id '13845'.</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:9" customHeight="0">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:18</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -879,321 +814,286 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653259' for the user with id '208503' for the grade item with id '13842'.</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I18" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:9" customHeight="0">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:38</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>Файл: Рабочая программа ВТ</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'resource' activity with course module id '2056915'.</t>
+          <t>The user with id '0' deleted the grade with id '61653258' for the user with id '208503' for the grade item with id '13839'.</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:9" customHeight="0">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:33</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>Страница: Список ссылок на источники материалов и/или правообладателей</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>Страница</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'page' activity with course module id '2056913'.</t>
+          <t>The user with id '0' deleted the grade with id '61653257' for the user with id '208503' for the grade item with id '13836'.</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:9" customHeight="0">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:30</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>Глоссарий: Глоссарий</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>Глоссарий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'glossary' activity with course module id '2056911'.</t>
+          <t>The user with id '0' deleted the grade with id '61653256' for the user with id '208503' for the grade item with id '13834'.</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:9" customHeight="0">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:27</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>Форум: Объявления</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
+          <t>The user with id '0' deleted the grade with id '61653255' for the user with id '208503' for the grade item with id '13830'.</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:9" customHeight="0">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:23</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум группы КИ 21-05б</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1343322'.</t>
+          <t>The user with id '0' deleted the grade with id '61653254' for the user with id '208503' for the grade item with id '13827'.</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I23" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:9" customHeight="0">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:11</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
+          <t>The user with id '0' deleted the grade with id '61653253' for the user with id '208503' for the grade item with id '13823'.</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I24" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:9" customHeight="0">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:59:54</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -1208,128 +1108,113 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653252' for the user with id '208503' for the grade item with id '13821'.</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I25" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:9" customHeight="0">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:56</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>Форум: Объявления</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '208503'.</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I26" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:9" customHeight="0">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:38</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
+          <t>The user with id '0' removed the user with id '208503' from the group with id '107485'.</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I27" s="0" t="inlineStr">
-        <is>
-          <t>82.146.19.243</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:9" customHeight="0">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:20</t>
+          <t>11/10/26, 09:29:58</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1344,17 +1229,17 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1364,14 +1249,14 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.243</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:9" customHeight="0">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:34</t>
+          <t>11/10/26, 09:29:56</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
@@ -1411,14 +1296,14 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:9" customHeight="0">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:29</t>
+          <t>11/10/26, 09:18:39</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
@@ -1458,14 +1343,14 @@
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:9" customHeight="0">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:22</t>
+          <t>11/10/26, 09:18:37</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
@@ -1485,17 +1370,17 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -1505,19 +1390,19 @@
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:9" customHeight="0">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 07:04:32</t>
+          <t>9/10/26, 20:27:09</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Сансызбай Нурбакыт -</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -1542,7 +1427,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '222555' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -1552,19 +1437,19 @@
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.153</t>
+          <t>91.79.229.252</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:9" customHeight="0">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 22:40:18</t>
+          <t>7/10/26, 05:48:36</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>Тимофеева Алина Андреевна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -1584,12 +1469,12 @@
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Просмотрено описание курса</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222888' viewed the course with id '1182'.</t>
+          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -1599,14 +1484,14 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>188.0.30.162</t>
+          <t>87.250.224.238</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:9" customHeight="0">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:56</t>
+          <t>4/10/26, 08:46:19</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
@@ -1653,7 +1538,7 @@
     <row r="35" spans="1:9" customHeight="0">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:28</t>
+          <t>4/10/26, 08:46:14</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
@@ -1700,7 +1585,7 @@
     <row r="36" spans="1:9" customHeight="0">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:12</t>
+          <t>4/10/26, 08:46:07</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
@@ -1747,17 +1632,17 @@
     <row r="37" spans="1:9" customHeight="0">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:45:22</t>
+          <t>3/10/26, 05:43:06</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Волков Даниил Феликсович</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -1772,39 +1657,34 @@
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '207098'.</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I37" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:9" customHeight="0">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:32</t>
+          <t>3/10/26, 05:43:06</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Волков Даниил Феликсович</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -1819,39 +1699,34 @@
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' assigned the role with id '4' to the user with id '168785'.</t>
+          <t>The user with id '0' enrolled the user with id '207098' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I38" s="0" t="inlineStr">
-        <is>
-          <t>176.116.179.187</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:9" customHeight="0">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:32</t>
+          <t>29/09/26, 10:16:16</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -1861,17 +1736,17 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' enrolled the user with id '168785' using the enrolment method 'manual' in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -1881,19 +1756,19 @@
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:9" customHeight="0">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:02</t>
+          <t>29/09/26, 10:16:12</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -1908,17 +1783,17 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -1928,19 +1803,19 @@
       </c>
       <c r="I40" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:9" customHeight="0">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:10:53</t>
+          <t>29/09/26, 10:16:04</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -1965,7 +1840,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -1975,24 +1850,24 @@
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:9" customHeight="0">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>29/09/26, 09:51:46</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -2007,34 +1882,39 @@
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '218267' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:9" customHeight="0">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>27/09/26, 06:56:31</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -2044,39 +1924,44 @@
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '218267' from the group with id '119772'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:9" customHeight="0">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>27/09/26, 06:56:26</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -2086,39 +1971,44 @@
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '218267'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:9" customHeight="0">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:26</t>
+          <t>27/09/26, 06:56:18</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -2133,286 +2023,321 @@
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '209842'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:9" customHeight="0">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:26</t>
+          <t>24/09/26, 17:00:38</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Рабочая программа ВТ</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '209842' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'resource' activity with course module id '2056915'.</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:9" customHeight="0">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 17:00:33</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Страница: Список ссылок на источники материалов и/или правообладателей</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Страница</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '209842' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'page' activity with course module id '2056913'.</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:9" customHeight="0">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 17:00:30</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Глоссарий: Глоссарий</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Глоссарий</t>
         </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971411' for the user with id '209842' for the grade item with id '712649'.</t>
+          <t>The user with id '222925' viewed the 'glossary' activity with course module id '2056911'.</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:9" customHeight="0">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 17:00:27</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Объявления</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971410' for the user with id '209842' for the grade item with id '666279'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:9" customHeight="0">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 17:00:23</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум группы КИ 21-05б</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971409' for the user with id '209842' for the grade item with id '524410'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1343322'.</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:9" customHeight="0">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 17:00:11</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971408' for the user with id '209842' for the grade item with id '212337'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:9" customHeight="0">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 16:59:54</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -2427,118 +2352,133 @@
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789133' for the user with id '209842' for the grade item with id '202565'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:9" customHeight="0">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 16:49:56</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Объявления</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789131' for the user with id '209842' for the grade item with id '202489'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:9" customHeight="0">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 16:49:38</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум</t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971407' for the user with id '209842' for the grade item with id '193468'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:9" customHeight="0">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 16:49:20</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -2553,34 +2493,39 @@
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971406' for the user with id '209842' for the grade item with id '162883'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:9" customHeight="0">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 12:05:34</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -2590,39 +2535,44 @@
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971405' for the user with id '209842' for the grade item with id '162882'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:9" customHeight="0">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 12:05:29</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -2632,39 +2582,44 @@
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789132' for the user with id '209842' for the grade item with id '162872'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:9" customHeight="0">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 12:05:22</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -2679,34 +2634,39 @@
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971404' for the user with id '209842' for the grade item with id '13852'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:9" customHeight="0">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>24/09/26, 07:04:32</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -2721,34 +2681,39 @@
       </c>
       <c r="F59" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971403' for the user with id '209842' for the grade item with id '13850'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>82.146.19.153</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:9" customHeight="0">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 22:40:18</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Тимофеева Алина Андреевна</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -2763,34 +2728,39 @@
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971402' for the user with id '209842' for the grade item with id '13847'.</t>
+          <t>The user with id '222888' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t>188.0.30.162</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:9" customHeight="0">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 17:50:56</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -2800,39 +2770,44 @@
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971401' for the user with id '209842' for the grade item with id '13845'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:9" customHeight="0">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 17:50:28</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -2842,39 +2817,44 @@
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971400' for the user with id '209842' for the grade item with id '13842'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:9" customHeight="0">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 17:50:12</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -2889,34 +2869,39 @@
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971399' for the user with id '209842' for the grade item with id '13839'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:9" customHeight="0">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 17:45:22</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -2931,34 +2916,39 @@
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971398' for the user with id '209842' for the grade item with id '13836'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:9" customHeight="0">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 15:11:32</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -2973,34 +2963,39 @@
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971397' for the user with id '209842' for the grade item with id '13834'.</t>
+          <t>The user with id '32194' assigned the role with id '4' to the user with id '168785'.</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:9" customHeight="0">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 15:11:32</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -3015,34 +3010,39 @@
       </c>
       <c r="F66" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971396' for the user with id '209842' for the grade item with id '13830'.</t>
+          <t>The user with id '32194' enrolled the user with id '168785' using the enrolment method 'manual' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:9" customHeight="0">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 15:11:02</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -3057,34 +3057,39 @@
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971395' for the user with id '209842' for the grade item with id '13827'.</t>
+          <t>The user with id '32194' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:9" customHeight="0">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>22/09/26, 15:10:53</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -3099,24 +3104,29 @@
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971393' for the user with id '209842' for the grade item with id '13823'.</t>
+          <t>The user with id '32194' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:9" customHeight="0">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
@@ -3126,7 +3136,7 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -3141,12 +3151,12 @@
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971394' for the user with id '209842' for the grade item with id '13821'.</t>
+          <t>The user with id '0' unenrolled the user with id '218267' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -3158,7 +3168,7 @@
     <row r="70" spans="1:9" customHeight="0">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
@@ -3168,7 +3178,7 @@
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -3183,12 +3193,12 @@
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '209842'.</t>
+          <t>The user with id '0' removed the user with id '218267' from the group with id '119772'.</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -3200,7 +3210,7 @@
     <row r="71" spans="1:9" customHeight="0">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
@@ -3210,7 +3220,7 @@
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -3225,12 +3235,12 @@
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '209842' from the group with id '107484'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '218267'.</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -3242,158 +3252,143 @@
     <row r="72" spans="1:9" customHeight="0">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:46</t>
+          <t>19/09/26, 05:44:26</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 1</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '24773'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '209842'.</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I72" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:9" customHeight="0">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:40</t>
+          <t>19/09/26, 05:44:26</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 15</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '601904'.</t>
+          <t>The user with id '0' enrolled the user with id '209842' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I73" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:9" customHeight="0">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:30</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 5</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '440558'.</t>
+          <t>The user with id '0' unenrolled the user with id '209842' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I74" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:9" customHeight="0">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:26</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -3408,39 +3403,34 @@
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971411' for the user with id '209842' for the grade item with id '712649'.</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I75" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:9" customHeight="0">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:21:20</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -3455,133 +3445,118 @@
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971410' for the user with id '209842' for the grade item with id '666279'.</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I76" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:9" customHeight="0">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:13</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the 'forum' activity with course module id '24770'.</t>
+          <t>The user with id '0' deleted the grade with id '61971409' for the user with id '209842' for the grade item with id '524410'.</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I77" s="0" t="inlineStr">
-        <is>
-          <t>66.90.91.206</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:9" customHeight="0">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:07</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум группы КИ 21-05б</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the 'forum' activity with course module id '1343322'.</t>
+          <t>The user with id '0' deleted the grade with id '61971408' for the user with id '209842' for the grade item with id '212337'.</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I78" s="0" t="inlineStr">
-        <is>
-          <t>66.90.91.206</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:9" customHeight="0">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:04</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -3596,29 +3571,24 @@
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '62789133' for the user with id '209842' for the grade item with id '202565'.</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I79" s="0" t="inlineStr">
-        <is>
-          <t>66.90.91.206</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:9" customHeight="0">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
@@ -3628,7 +3598,7 @@
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -3643,12 +3613,12 @@
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t>Член группы добавлен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' added the user with id '176234' to the group with id '107484'.</t>
+          <t>The user with id '0' deleted the grade with id '62789131' for the user with id '209842' for the grade item with id '202489'.</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -3660,7 +3630,7 @@
     <row r="81" spans="1:9" customHeight="0">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
@@ -3670,7 +3640,7 @@
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -3685,12 +3655,12 @@
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '176234'.</t>
+          <t>The user with id '0' deleted the grade with id '61971407' for the user with id '209842' for the grade item with id '193468'.</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -3702,7 +3672,7 @@
     <row r="82" spans="1:9" customHeight="0">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
@@ -3712,7 +3682,7 @@
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -3727,12 +3697,12 @@
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '176234' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971406' for the user with id '209842' for the grade item with id '162883'.</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -3744,17 +3714,17 @@
     <row r="83" spans="1:9" customHeight="0">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 07:24:42</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -3769,86 +3739,76 @@
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971405' for the user with id '209842' for the grade item with id '162882'.</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I83" s="0" t="inlineStr">
-        <is>
-          <t>176.59.134.231</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:9" customHeight="0">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 01:47:10</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>Файл: Вопросы к экзамену КИ23-03, КИ23-04, КИ23-05</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the 'resource' activity with course module id '548778'.</t>
+          <t>The user with id '0' deleted the grade with id '62789132' for the user with id '209842' for the grade item with id '162872'.</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I84" s="0" t="inlineStr">
-        <is>
-          <t>176.116.166.86</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:9" customHeight="0">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 01:43:34</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -3863,39 +3823,34 @@
       </c>
       <c r="F85" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971404' for the user with id '209842' for the grade item with id '13852'.</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I85" s="0" t="inlineStr">
-        <is>
-          <t>176.116.166.86</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:9" customHeight="0">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:27:38</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -3910,39 +3865,34 @@
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the profile for the user with id '222427' in the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971403' for the user with id '209842' for the grade item with id '13850'.</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I86" s="0" t="inlineStr">
-        <is>
-          <t>10.3.73.136</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:9" customHeight="0">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:35</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -3957,39 +3907,34 @@
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the profile for the user with id '222375' in the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971402' for the user with id '209842' for the grade item with id '13847'.</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I87" s="0" t="inlineStr">
-        <is>
-          <t>10.3.73.136</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:9" customHeight="0">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:16</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -4004,39 +3949,34 @@
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971401' for the user with id '209842' for the grade item with id '13845'.</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I88" s="0" t="inlineStr">
-        <is>
-          <t>10.3.73.136</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:9" customHeight="0">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:10</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -4051,39 +3991,34 @@
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971400' for the user with id '209842' for the grade item with id '13842'.</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I89" s="0" t="inlineStr">
-        <is>
-          <t>10.3.73.136</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:9" customHeight="0">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 11:39:31</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -4098,39 +4033,34 @@
       </c>
       <c r="F90" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971399' for the user with id '209842' for the grade item with id '13839'.</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I90" s="0" t="inlineStr">
-        <is>
-          <t>176.59.145.192</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:9" customHeight="0">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t>12/09/26, 16:36:10</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>Моисеев Никита Андреевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -4145,39 +4075,34 @@
       </c>
       <c r="F91" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222376' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971398' for the user with id '209842' for the grade item with id '13836'.</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I91" s="0" t="inlineStr">
-        <is>
-          <t>188.0.28.144</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:9" customHeight="0">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t>11/09/26, 20:05:31</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>Рагозина Виктория Викторовна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -4192,39 +4117,34 @@
       </c>
       <c r="F92" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198852' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971397' for the user with id '209842' for the grade item with id '13834'.</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I92" s="0" t="inlineStr">
-        <is>
-          <t>188.0.28.220</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:9" customHeight="0">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t>11/09/26, 16:10:19</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -4239,29 +4159,24 @@
       </c>
       <c r="F93" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971396' for the user with id '209842' for the grade item with id '13830'.</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I93" s="0" t="inlineStr">
-        <is>
-          <t>176.59.133.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:9" customHeight="0">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B94" s="0" t="inlineStr">
@@ -4271,7 +4186,7 @@
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -4286,12 +4201,12 @@
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '217794' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61971395' for the user with id '209842' for the grade item with id '13827'.</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -4303,7 +4218,7 @@
     <row r="95" spans="1:9" customHeight="0">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B95" s="0" t="inlineStr">
@@ -4313,7 +4228,7 @@
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -4328,12 +4243,12 @@
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '217794' from the group with id '119772'.</t>
+          <t>The user with id '0' deleted the grade with id '61971393' for the user with id '209842' for the grade item with id '13823'.</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -4345,7 +4260,7 @@
     <row r="96" spans="1:9" customHeight="0">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B96" s="0" t="inlineStr">
@@ -4355,7 +4270,7 @@
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -4370,12 +4285,12 @@
       </c>
       <c r="F96" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '217794'.</t>
+          <t>The user with id '0' deleted the grade with id '61971394' for the user with id '209842' for the grade item with id '13821'.</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -4387,64 +4302,59 @@
     <row r="97" spans="1:9" customHeight="0">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:41:03</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t>Файл: Описание режима обучения</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the 'resource' activity with course module id '2056918'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '209842'.</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I97" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:9" customHeight="0">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:58</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -4459,34 +4369,29 @@
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the course with id '1182'.</t>
+          <t>The user with id '0' removed the user with id '209842' from the group with id '107484'.</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I98" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:9" customHeight="0">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:50</t>
+          <t>17/09/26, 20:33:46</t>
         </is>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -4496,7 +4401,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Тест: Задачи к лекции 1</t>
         </is>
       </c>
       <c r="E99" s="0" t="inlineStr">
@@ -4506,12 +4411,12 @@
       </c>
       <c r="F99" s="0" t="inlineStr">
         <is>
-          <t>Отчет по тесту просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '24773'.</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -4521,19 +4426,19 @@
       </c>
       <c r="I99" s="0" t="inlineStr">
         <is>
-          <t>10.128.134.198</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:9" customHeight="0">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:39</t>
+          <t>17/09/26, 20:33:40</t>
         </is>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -4543,7 +4448,7 @@
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Тест: Задачи к лекции 15</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr">
@@ -4553,12 +4458,12 @@
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t>Отчет по тесту просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '601904'.</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -4568,19 +4473,19 @@
       </c>
       <c r="I100" s="0" t="inlineStr">
         <is>
-          <t>10.128.134.198</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:9" customHeight="0">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:25</t>
+          <t>17/09/26, 20:33:30</t>
         </is>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -4590,7 +4495,7 @@
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Тест: Задачи к лекции 5</t>
         </is>
       </c>
       <c r="E101" s="0" t="inlineStr">
@@ -4605,7 +4510,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the 'quiz' activity with course module id '24836'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '440558'.</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -4615,19 +4520,19 @@
       </c>
       <c r="I101" s="0" t="inlineStr">
         <is>
-          <t>10.128.134.198</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:9" customHeight="0">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:48</t>
+          <t>17/09/26, 20:33:26</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -4652,7 +4557,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -4662,24 +4567,24 @@
       </c>
       <c r="I102" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:9" customHeight="0">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:43</t>
+          <t>17/09/26, 20:21:20</t>
         </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -4694,12 +4599,12 @@
       </c>
       <c r="F103" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' unenrolled the user with id '237748' using the enrolment method 'manual' from the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -4709,44 +4614,44 @@
       </c>
       <c r="I103" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:9" customHeight="0">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:43</t>
+          <t>17/09/26, 00:35:13</t>
         </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум</t>
         </is>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' unassigned the role with id '5' from the user with id '237748'.</t>
+          <t>The user with id '222427' viewed the 'forum' activity with course module id '24770'.</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -4756,19 +4661,19 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:9" customHeight="0">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:28</t>
+          <t>17/09/26, 00:35:07</t>
         </is>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -4778,22 +4683,22 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум группы КИ 21-05б</t>
         </is>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F105" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '222427' viewed the 'forum' activity with course module id '1343322'.</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -4803,24 +4708,24 @@
       </c>
       <c r="I105" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:9" customHeight="0">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:05:46</t>
+          <t>17/09/26, 00:35:04</t>
         </is>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -4835,12 +4740,12 @@
       </c>
       <c r="F106" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' removed the user with id '237748' from the group with id '118487'.</t>
+          <t>The user with id '222427' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -4850,24 +4755,24 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:9" customHeight="0">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:05:01</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -4887,34 +4792,29 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' added the user with id '237748' to the group with id '118487'.</t>
+          <t>The user with id '0' added the user with id '176234' to the group with id '107484'.</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I107" s="0" t="inlineStr">
-        <is>
-          <t>10.3.73.136</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:9" customHeight="0">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:57</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
@@ -4929,39 +4829,34 @@
       </c>
       <c r="F108" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '176234'.</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I108" s="0" t="inlineStr">
-        <is>
-          <t>10.3.73.136</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:9" customHeight="0">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:50</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -4976,39 +4871,34 @@
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' assigned the role with id '5' to the user with id '237748'.</t>
+          <t>The user with id '0' enrolled the user with id '176234' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I109" s="0" t="inlineStr">
-        <is>
-          <t>10.3.73.136</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:9" customHeight="0">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:50</t>
+          <t>16/09/26, 07:24:42</t>
         </is>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -5023,12 +4913,12 @@
       </c>
       <c r="F110" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' enrolled the user with id '237748' using the enrolment method 'manual' in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -5038,19 +4928,19 @@
       </c>
       <c r="I110" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.59.134.231</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:9" customHeight="0">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:02:43</t>
+          <t>16/09/26, 01:47:10</t>
         </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -5060,22 +4950,22 @@
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Вопросы к экзамену КИ23-03, КИ23-04, КИ23-05</t>
         </is>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F111" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the 'resource' activity with course module id '548778'.</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -5085,19 +4975,19 @@
       </c>
       <c r="I111" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.116.166.86</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:9" customHeight="0">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:02:39</t>
+          <t>16/09/26, 01:43:34</t>
         </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -5122,7 +5012,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -5132,24 +5022,24 @@
       </c>
       <c r="I112" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.116.166.86</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:9" customHeight="0">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 11:42:02</t>
+          <t>14/09/26, 14:27:38</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>Лаушкин Григорий Вадимович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -5164,12 +5054,12 @@
       </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>The user with id '207594' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the profile for the user with id '222427' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -5179,14 +5069,14 @@
       </c>
       <c r="I113" s="0" t="inlineStr">
         <is>
-          <t>10.30.102.26</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:9" customHeight="0">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>3/09/26, 13:49:56</t>
+          <t>14/09/26, 14:26:35</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
@@ -5196,7 +5086,7 @@
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -5211,12 +5101,12 @@
       </c>
       <c r="F114" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the section with id '12702'.</t>
+          <t>The user with id '20261' viewed the profile for the user with id '222375' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -5233,7 +5123,7 @@
     <row r="115" spans="1:9" customHeight="0">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>3/09/26, 13:49:45</t>
+          <t>14/09/26, 14:26:16</t>
         </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
@@ -5258,12 +5148,12 @@
       </c>
       <c r="F115" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -5280,12 +5170,12 @@
     <row r="116" spans="1:9" customHeight="0">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 18:03:03</t>
+          <t>14/09/26, 14:26:10</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>Попова Виктория Максимовна</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -5295,22 +5185,22 @@
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 5</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F116" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221894' viewed the 'quiz' activity with course module id '440558'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -5320,19 +5210,19 @@
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.152</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:9" customHeight="0">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 18:02:48</t>
+          <t>14/09/26, 11:39:31</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>Попова Виктория Максимовна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -5357,7 +5247,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221894' viewed the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -5367,19 +5257,19 @@
       </c>
       <c r="I117" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.152</t>
+          <t>176.59.145.192</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:9" customHeight="0">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 03:09:22</t>
+          <t>12/09/26, 16:36:10</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>Ярусов Семён Александрович</t>
+          <t>Моисеев Никита Андреевич</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -5404,7 +5294,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222505' viewed the course with id '1182'.</t>
+          <t>The user with id '222376' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -5414,24 +5304,24 @@
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>10.132.0.234</t>
+          <t>188.0.28.144</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:9" customHeight="0">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>31/08/26, 17:07:41</t>
+          <t>11/09/26, 20:05:31</t>
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>Рагозина Виктория Викторовна</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -5441,17 +5331,17 @@
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
-          <t>Отчет по пользователю</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F119" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Отчет по пользователю» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>The user with id '217787' viewed the user report in the gradebook.</t>
+          <t>The user with id '198852' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -5461,19 +5351,19 @@
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>89.113.136.51</t>
+          <t>188.0.28.220</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:9" customHeight="0">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>31/08/26, 17:07:36</t>
+          <t>11/09/26, 16:10:19</t>
         </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -5498,7 +5388,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>The user with id '217787' viewed the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -5508,24 +5398,24 @@
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>89.113.136.51</t>
+          <t>176.59.133.133</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:9" customHeight="0">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 18:46:50</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>Николаев Виктор Анатольевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -5540,86 +5430,76 @@
       </c>
       <c r="F121" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221862' viewed the course with id '1182'.</t>
+          <t>The user with id '0' unenrolled the user with id '217794' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I121" s="0" t="inlineStr">
-        <is>
-          <t>176.59.130.167</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:9" customHeight="0">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:06:13</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F122" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the 'resource' activity with course module id '24771'.</t>
+          <t>The user with id '0' removed the user with id '217794' from the group with id '119772'.</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I122" s="0" t="inlineStr">
-        <is>
-          <t>10.30.119.34</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:9" customHeight="0">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:05:42</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -5634,59 +5514,54 @@
       </c>
       <c r="F123" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the course with id '1182'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '217794'.</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I123" s="0" t="inlineStr">
-        <is>
-          <t>10.30.119.34</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:9" customHeight="0">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:05:39</t>
+          <t>9/09/26, 09:41:03</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Тисецкая Анастасия Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Описание режима обучения</t>
         </is>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the profile for the user with id '196462' in the course with id '1182'.</t>
+          <t>The user with id '115989' viewed the 'resource' activity with course module id '2056918'.</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -5696,44 +5571,44 @@
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>10.30.119.34</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:9" customHeight="0">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:29</t>
+          <t>9/09/26, 09:40:58</t>
         </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 6</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
-          <t>Завершенная попытка теста просмотрена</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' has reviewed quiz attempt with id '9161794' by user with id '218896' for the quiz with course module id '24797'.</t>
+          <t>The user with id '115989' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -5743,19 +5618,19 @@
       </c>
       <c r="I125" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:9" customHeight="0">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:23</t>
+          <t>9/09/26, 09:40:50</t>
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -5765,7 +5640,7 @@
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 6</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E126" s="0" t="inlineStr">
@@ -5775,12 +5650,12 @@
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Отчет по тесту просмотрен</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the 'quiz' activity with course module id '24797'.</t>
+          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -5790,44 +5665,44 @@
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:9" customHeight="0">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:11</t>
+          <t>9/09/26, 09:40:39</t>
         </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
-          <t>Отчет по участнику курса просмотрен</t>
+          <t>Отчет по тесту просмотрен</t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the user report for the course with id '1182' for user with id '218896'.</t>
+          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -5837,19 +5712,19 @@
       </c>
       <c r="I127" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:9" customHeight="0">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:47:40</t>
+          <t>9/09/26, 09:40:25</t>
         </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -5859,22 +5734,22 @@
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the course with id '1182'.</t>
+          <t>The user with id '115989' viewed the 'quiz' activity with course module id '24836'.</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -5884,19 +5759,19 @@
       </c>
       <c r="I128" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:9" customHeight="0">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t>28/08/26, 14:05:02</t>
+          <t>7/09/26, 12:06:48</t>
         </is>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>Шишигин Никита Геннадьевич</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -5921,7 +5796,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>The user with id '220735' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -5931,24 +5806,24 @@
       </c>
       <c r="I129" s="0" t="inlineStr">
         <is>
-          <t>91.132.20.254</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:9" customHeight="0">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t>26/08/26, 20:49:54</t>
+          <t>7/09/26, 12:06:43</t>
         </is>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -5963,12 +5838,12 @@
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t>Просмотрено описание курса</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
+          <t>The user with id '20261' unenrolled the user with id '237748' using the enrolment method 'manual' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -5978,24 +5853,24 @@
       </c>
       <c r="I130" s="0" t="inlineStr">
         <is>
-          <t>5.255.231.81</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:9" customHeight="0">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t>20/08/26, 23:30:20</t>
+          <t>7/09/26, 12:06:43</t>
         </is>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>Ооржак Анчы Вячеславович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -6010,12 +5885,12 @@
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222788' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '20261' unassigned the role with id '5' from the user with id '237748'.</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -6025,19 +5900,19 @@
       </c>
       <c r="I131" s="0" t="inlineStr">
         <is>
-          <t>185.193.199.22</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:9" customHeight="0">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>20/08/26, 23:30:17</t>
+          <t>7/09/26, 12:06:28</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>Ооржак Анчы Вячеславович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -6057,12 +5932,12 @@
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222788' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -6072,14 +5947,14 @@
       </c>
       <c r="I132" s="0" t="inlineStr">
         <is>
-          <t>185.193.199.22</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:9" customHeight="0">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:26</t>
+          <t>7/09/26, 12:05:46</t>
         </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
@@ -6089,7 +5964,7 @@
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -6104,12 +5979,12 @@
       </c>
       <c r="F133" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' removed the user with id '237748' from the group with id '118487'.</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -6126,7 +6001,7 @@
     <row r="134" spans="1:9" customHeight="0">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:23</t>
+          <t>7/09/26, 12:05:01</t>
         </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
@@ -6136,7 +6011,7 @@
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
@@ -6151,12 +6026,12 @@
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Член группы добавлен</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' added the user with id '237748' to the group with id '118487'.</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -6173,7 +6048,7 @@
     <row r="135" spans="1:9" customHeight="0">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:22</t>
+          <t>7/09/26, 12:03:57</t>
         </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
@@ -6198,12 +6073,12 @@
       </c>
       <c r="F135" s="0" t="inlineStr">
         <is>
-          <t>Курс обновлен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' updated the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -6220,7 +6095,7 @@
     <row r="136" spans="1:9" customHeight="0">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:40</t>
+          <t>7/09/26, 12:03:50</t>
         </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
@@ -6230,7 +6105,7 @@
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
@@ -6245,12 +6120,12 @@
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' assigned the role with id '5' to the user with id '237748'.</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -6267,7 +6142,7 @@
     <row r="137" spans="1:9" customHeight="0">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:20</t>
+          <t>7/09/26, 12:03:50</t>
         </is>
       </c>
       <c r="B137" s="0" t="inlineStr">
@@ -6277,7 +6152,7 @@
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -6292,12 +6167,12 @@
       </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' enrolled the user with id '237748' using the enrolment method 'manual' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -6314,7 +6189,7 @@
     <row r="138" spans="1:9" customHeight="0">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:12</t>
+          <t>7/09/26, 12:02:43</t>
         </is>
       </c>
       <c r="B138" s="0" t="inlineStr">
@@ -6339,12 +6214,12 @@
       </c>
       <c r="F138" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -6361,7 +6236,7 @@
     <row r="139" spans="1:9" customHeight="0">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:12</t>
+          <t>7/09/26, 12:02:39</t>
         </is>
       </c>
       <c r="B139" s="0" t="inlineStr">
@@ -6386,12 +6261,12 @@
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
-          <t>Курс обновлен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' updated the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -6408,12 +6283,12 @@
     <row r="140" spans="1:9" customHeight="0">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:55</t>
+          <t>7/09/26, 11:42:02</t>
         </is>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Лаушкин Григорий Вадимович</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -6438,7 +6313,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '207594' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -6448,14 +6323,14 @@
       </c>
       <c r="I140" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>10.30.102.26</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:9" customHeight="0">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:17</t>
+          <t>3/09/26, 13:49:56</t>
         </is>
       </c>
       <c r="B141" s="0" t="inlineStr">
@@ -6480,12 +6355,12 @@
       </c>
       <c r="F141" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Раздел просмотрен</t>
         </is>
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the section with id '12702'.</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -6502,7 +6377,7 @@
     <row r="142" spans="1:9" customHeight="0">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:03</t>
+          <t>3/09/26, 13:49:45</t>
         </is>
       </c>
       <c r="B142" s="0" t="inlineStr">
@@ -6549,12 +6424,12 @@
     <row r="143" spans="1:9" customHeight="0">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:20:38</t>
+          <t>2/09/26, 18:03:03</t>
         </is>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Попова Виктория Максимовна</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -6564,22 +6439,22 @@
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 5</t>
         </is>
       </c>
       <c r="E143" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F143" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '221894' viewed the 'quiz' activity with course module id '440558'.</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -6589,19 +6464,19 @@
       </c>
       <c r="I143" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>188.0.28.152</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:9" customHeight="0">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t>17/08/26, 13:54:23</t>
+          <t>2/09/26, 18:02:48</t>
         </is>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>Гудин Степан Денисович</t>
+          <t>Попова Виктория Максимовна</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -6611,22 +6486,22 @@
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 2</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E144" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F144" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222257' viewed the 'quiz' activity with course module id '24778'.</t>
+          <t>The user with id '221894' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -6636,19 +6511,19 @@
       </c>
       <c r="I144" s="0" t="inlineStr">
         <is>
-          <t>10.28.71.178</t>
+          <t>188.0.28.152</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:9" customHeight="0">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t>17/08/26, 13:54:13</t>
+          <t>2/09/26, 03:09:22</t>
         </is>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>Гудин Степан Денисович</t>
+          <t>Ярусов Семён Александрович</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -6673,7 +6548,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222257' viewed the course with id '1182'.</t>
+          <t>The user with id '222505' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -6683,24 +6558,24 @@
       </c>
       <c r="I145" s="0" t="inlineStr">
         <is>
-          <t>10.28.71.178</t>
+          <t>10.132.0.234</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:9" customHeight="0">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 19:11:54</t>
+          <t>31/08/26, 17:07:41</t>
         </is>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -6710,17 +6585,17 @@
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Отчет по пользователю</t>
         </is>
       </c>
       <c r="F146" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Отчет по пользователю» просмотрен</t>
         </is>
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '217787' viewed the user report in the gradebook.</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -6730,19 +6605,19 @@
       </c>
       <c r="I146" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>89.113.136.51</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:9" customHeight="0">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 17:28:04</t>
+          <t>31/08/26, 17:07:36</t>
         </is>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -6752,22 +6627,22 @@
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F147" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'resource' activity with course module id '24771'.</t>
+          <t>The user with id '217787' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -6777,19 +6652,19 @@
       </c>
       <c r="I147" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>89.113.136.51</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:9" customHeight="0">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 17:23:59</t>
+          <t>30/08/26, 18:46:50</t>
         </is>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Николаев Виктор Анатольевич</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -6814,7 +6689,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '221862' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -6824,19 +6699,19 @@
       </c>
       <c r="I148" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>176.59.130.167</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:9" customHeight="0">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:25</t>
+          <t>30/08/26, 01:06:13</t>
         </is>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -6846,22 +6721,22 @@
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
         </is>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '171426'.</t>
+          <t>The user with id '198420' viewed the 'resource' activity with course module id '24771'.</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -6871,19 +6746,19 @@
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:9" customHeight="0">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:21</t>
+          <t>30/08/26, 01:05:42</t>
         </is>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -6893,22 +6768,22 @@
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 8. Формула Грина. Независимость криволинейного интеграла 2-го рода от пути интегрирования</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F150" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '440562'.</t>
+          <t>The user with id '198420' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -6918,24 +6793,24 @@
       </c>
       <c r="I150" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:9" customHeight="0">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:09</t>
+          <t>30/08/26, 01:05:39</t>
         </is>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Тисецкая Анастасия Александровна</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -6950,12 +6825,12 @@
       </c>
       <c r="F151" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12711'.</t>
+          <t>The user with id '198420' viewed the profile for the user with id '196462' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -6965,44 +6840,44 @@
       </c>
       <c r="I151" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:9" customHeight="0">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:05</t>
+          <t>29/08/26, 21:48:29</t>
         </is>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 6</t>
         </is>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F152" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Завершенная попытка теста просмотрена</t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12714'.</t>
+          <t>The user with id '218896' has reviewed quiz attempt with id '9161794' by user with id '218896' for the quiz with course module id '24797'.</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -7012,19 +6887,19 @@
       </c>
       <c r="I152" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:9" customHeight="0">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:01</t>
+          <t>29/08/26, 21:48:23</t>
         </is>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -7034,12 +6909,12 @@
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 16. Функциональные ряды. Основные понятия. Степенные ряды. Свойства степенных рядов. Разложение функции в степенные ряды. Ряд Тейлора. Ряд Маклорена</t>
+          <t>Тест: Задачи к лекции 6</t>
         </is>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F153" s="0" t="inlineStr">
@@ -7049,7 +6924,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '440645'.</t>
+          <t>The user with id '218896' viewed the 'quiz' activity with course module id '24797'.</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -7059,24 +6934,24 @@
       </c>
       <c r="I153" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:9" customHeight="0">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:56</t>
+          <t>29/08/26, 21:48:11</t>
         </is>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -7091,12 +6966,12 @@
       </c>
       <c r="F154" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Отчет по участнику курса просмотрен</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12706'.</t>
+          <t>The user with id '218896' viewed the user report for the course with id '1182' for user with id '218896'.</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -7106,19 +6981,19 @@
       </c>
       <c r="I154" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:9" customHeight="0">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:47</t>
+          <t>29/08/26, 21:47:40</t>
         </is>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -7128,22 +7003,22 @@
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 2.  Дифференцируемость и полный дифференциал ФНП. Дифференциалы высших порядков. Производная сложной функции. Производная неявной функции. Производная по направлению. Градиент</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F155" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '24776'.</t>
+          <t>The user with id '218896' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -7153,19 +7028,19 @@
       </c>
       <c r="I155" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:9" customHeight="0">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:40</t>
+          <t>28/08/26, 14:05:02</t>
         </is>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Шишигин Никита Геннадьевич</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -7190,7 +7065,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the course with id '1182'.</t>
+          <t>The user with id '220735' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -7200,19 +7075,19 @@
       </c>
       <c r="I156" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>91.132.20.254</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:9" customHeight="0">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t>31/07/26, 13:15:41</t>
+          <t>26/08/26, 20:49:54</t>
         </is>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>Войченко Антон Дмитриевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -7232,12 +7107,12 @@
       </c>
       <c r="F157" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Просмотрено описание курса</t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218660' viewed the course with id '1182'.</t>
+          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -7247,19 +7122,19 @@
       </c>
       <c r="I157" s="0" t="inlineStr">
         <is>
-          <t>193.8.74.6</t>
+          <t>5.255.231.81</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:9" customHeight="0">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t>16/07/26, 16:23:26</t>
+          <t>20/08/26, 23:30:20</t>
         </is>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>Администратор системы</t>
+          <t>Ооржак Анчы Вячеславович</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -7269,7 +7144,7 @@
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E158" s="0" t="inlineStr">
@@ -7279,29 +7154,34 @@
       </c>
       <c r="F158" s="0" t="inlineStr">
         <is>
-          <t>Вопрос удален</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>The user with id '2' deleted the question with id '103599' from the category with the id '7395'.</t>
+          <t>The user with id '222788' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I158" s="0" t="inlineStr">
+        <is>
+          <t>185.193.199.22</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:9" customHeight="0">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t>16/07/26, 16:23:26</t>
+          <t>20/08/26, 23:30:17</t>
         </is>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>Администратор системы</t>
+          <t>Ооржак Анчы Вячеславович</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -7311,7 +7191,7 @@
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
-          <t>Банк вопросов: Математический анализ (Часть 2) - общий банк вопросов</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E159" s="0" t="inlineStr">
@@ -7321,57 +7201,1321 @@
       </c>
       <c r="F159" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса создан</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>The user with id '2' created the 'qbank' activity with course module id '2058071'.</t>
+          <t>The user with id '222788' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I159" s="0" t="inlineStr">
+        <is>
+          <t>185.193.199.22</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:9" customHeight="0">
       <c r="A160" s="0" t="inlineStr">
         <is>
+          <t>18/08/26, 12:27:26</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E160" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F160" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G160" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H160" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I160" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" spans="1:9" customHeight="0">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:27:23</t>
+        </is>
+      </c>
+      <c r="B161" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D161" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E161" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F161" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G161" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H161" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I161" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" spans="1:9" customHeight="0">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:27:22</t>
+        </is>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E162" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F162" s="0" t="inlineStr">
+        <is>
+          <t>Курс обновлен</t>
+        </is>
+      </c>
+      <c r="G162" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' updated the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H162" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I162" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" spans="1:9" customHeight="0">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:26:40</t>
+        </is>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D163" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E163" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F163" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G163" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H163" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I163" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" spans="1:9" customHeight="0">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:26:20</t>
+        </is>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D164" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E164" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F164" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G164" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H164" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I164" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" spans="1:9" customHeight="0">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:26:12</t>
+        </is>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D165" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E165" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F165" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G165" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H165" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I165" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" spans="1:9" customHeight="0">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:26:12</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D166" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E166" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F166" s="0" t="inlineStr">
+        <is>
+          <t>Курс обновлен</t>
+        </is>
+      </c>
+      <c r="G166" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' updated the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H166" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I166" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" spans="1:9" customHeight="0">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:21:55</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D167" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E167" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F167" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G167" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H167" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I167" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" spans="1:9" customHeight="0">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:21:17</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E168" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F168" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G168" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H168" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I168" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" spans="1:9" customHeight="0">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:21:03</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F169" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G169" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H169" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I169" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" spans="1:9" customHeight="0">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>18/08/26, 12:20:38</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F170" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G170" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H170" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I170" s="0" t="inlineStr">
+        <is>
+          <t>10.3.73.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" spans="1:9" customHeight="0">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>17/08/26, 13:54:23</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>Гудин Степан Денисович</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t>Тест: Задачи к лекции 2</t>
+        </is>
+      </c>
+      <c r="E171" s="0" t="inlineStr">
+        <is>
+          <t>Тест</t>
+        </is>
+      </c>
+      <c r="F171" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса просмотрен</t>
+        </is>
+      </c>
+      <c r="G171" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '222257' viewed the 'quiz' activity with course module id '24778'.</t>
+        </is>
+      </c>
+      <c r="H171" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I171" s="0" t="inlineStr">
+        <is>
+          <t>10.28.71.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" spans="1:9" customHeight="0">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>17/08/26, 13:54:13</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>Гудин Степан Денисович</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E172" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F172" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G172" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '222257' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H172" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I172" s="0" t="inlineStr">
+        <is>
+          <t>10.28.71.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" spans="1:9" customHeight="0">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 19:11:54</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>Яцинович Антон Николаевич</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E173" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F173" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G173" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H173" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I173" s="0" t="inlineStr">
+        <is>
+          <t>176.49.89.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" spans="1:9" customHeight="0">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 17:28:04</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>Яцинович Антон Николаевич</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
+        </is>
+      </c>
+      <c r="E174" s="0" t="inlineStr">
+        <is>
+          <t>Файл</t>
+        </is>
+      </c>
+      <c r="F174" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса просмотрен</t>
+        </is>
+      </c>
+      <c r="G174" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '222925' viewed the 'resource' activity with course module id '24771'.</t>
+        </is>
+      </c>
+      <c r="H174" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I174" s="0" t="inlineStr">
+        <is>
+          <t>176.49.89.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" spans="1:9" customHeight="0">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 17:23:59</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>Яцинович Антон Николаевич</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E175" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F175" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G175" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H175" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I175" s="0" t="inlineStr">
+        <is>
+          <t>176.49.89.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" spans="1:9" customHeight="0">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:10:25</t>
+        </is>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E176" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F176" s="0" t="inlineStr">
+        <is>
+          <t>Раздел просмотрен</t>
+        </is>
+      </c>
+      <c r="G176" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the section with id '171426'.</t>
+        </is>
+      </c>
+      <c r="H176" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I176" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" spans="1:9" customHeight="0">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:10:21</t>
+        </is>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>Файл: Лекция 8. Формула Грина. Независимость криволинейного интеграла 2-го рода от пути интегрирования</t>
+        </is>
+      </c>
+      <c r="E177" s="0" t="inlineStr">
+        <is>
+          <t>Файл</t>
+        </is>
+      </c>
+      <c r="F177" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса просмотрен</t>
+        </is>
+      </c>
+      <c r="G177" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '440562'.</t>
+        </is>
+      </c>
+      <c r="H177" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I177" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" spans="1:9" customHeight="0">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:10:09</t>
+        </is>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F178" s="0" t="inlineStr">
+        <is>
+          <t>Раздел просмотрен</t>
+        </is>
+      </c>
+      <c r="G178" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the section with id '12711'.</t>
+        </is>
+      </c>
+      <c r="H178" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I178" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" spans="1:9" customHeight="0">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:10:05</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F179" s="0" t="inlineStr">
+        <is>
+          <t>Раздел просмотрен</t>
+        </is>
+      </c>
+      <c r="G179" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the section with id '12714'.</t>
+        </is>
+      </c>
+      <c r="H179" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I179" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" spans="1:9" customHeight="0">
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:10:01</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>Файл: Лекция 16. Функциональные ряды. Основные понятия. Степенные ряды. Свойства степенных рядов. Разложение функции в степенные ряды. Ряд Тейлора. Ряд Маклорена</t>
+        </is>
+      </c>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t>Файл</t>
+        </is>
+      </c>
+      <c r="F180" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса просмотрен</t>
+        </is>
+      </c>
+      <c r="G180" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '440645'.</t>
+        </is>
+      </c>
+      <c r="H180" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I180" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" spans="1:9" customHeight="0">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:09:56</t>
+        </is>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E181" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F181" s="0" t="inlineStr">
+        <is>
+          <t>Раздел просмотрен</t>
+        </is>
+      </c>
+      <c r="G181" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the section with id '12706'.</t>
+        </is>
+      </c>
+      <c r="H181" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I181" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" spans="1:9" customHeight="0">
+      <c r="A182" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:09:47</t>
+        </is>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t>Файл: Лекция 2.  Дифференцируемость и полный дифференциал ФНП. Дифференциалы высших порядков. Производная сложной функции. Производная неявной функции. Производная по направлению. Градиент</t>
+        </is>
+      </c>
+      <c r="E182" s="0" t="inlineStr">
+        <is>
+          <t>Файл</t>
+        </is>
+      </c>
+      <c r="F182" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса просмотрен</t>
+        </is>
+      </c>
+      <c r="G182" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '24776'.</t>
+        </is>
+      </c>
+      <c r="H182" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I182" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" spans="1:9" customHeight="0">
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t>16/08/26, 00:09:40</t>
+        </is>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>Марков Сергей Денисович</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F183" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G183" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '223842' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H183" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I183" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" spans="1:9" customHeight="0">
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t>31/07/26, 13:15:41</t>
+        </is>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>Войченко Антон Дмитриевич</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E184" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F184" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G184" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '218660' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H184" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I184" s="0" t="inlineStr">
+        <is>
+          <t>193.8.74.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" spans="1:9" customHeight="0">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
           <t>16/07/26, 16:23:26</t>
         </is>
       </c>
-      <c r="B160" s="0" t="inlineStr">
+      <c r="B185" s="0" t="inlineStr">
         <is>
           <t>Администратор системы</t>
         </is>
       </c>
-      <c r="C160" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D160" s="0" t="inlineStr">
-        <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
-        </is>
-      </c>
-      <c r="E160" s="0" t="inlineStr">
-        <is>
-          <t>Система</t>
-        </is>
-      </c>
-      <c r="F160" s="0" t="inlineStr">
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t>Тест: Задачи к лекции 14</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F185" s="0" t="inlineStr">
         <is>
           <t>Вопрос удален</t>
         </is>
       </c>
-      <c r="G160" s="0" t="inlineStr">
+      <c r="G185" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '2' deleted the question with id '103599' from the category with the id '7395'.</t>
+        </is>
+      </c>
+      <c r="H185" s="0" t="inlineStr">
+        <is>
+          <t>cli</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" spans="1:9" customHeight="0">
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t>16/07/26, 16:23:26</t>
+        </is>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t>Администратор системы</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t>Банк вопросов: Математический анализ (Часть 2) - общий банк вопросов</t>
+        </is>
+      </c>
+      <c r="E186" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F186" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса создан</t>
+        </is>
+      </c>
+      <c r="G186" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '2' created the 'qbank' activity with course module id '2058071'.</t>
+        </is>
+      </c>
+      <c r="H186" s="0" t="inlineStr">
+        <is>
+          <t>cli</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" spans="1:9" customHeight="0">
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t>16/07/26, 16:23:26</t>
+        </is>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t>Администратор системы</t>
+        </is>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F187" s="0" t="inlineStr">
+        <is>
+          <t>Вопрос удален</t>
+        </is>
+      </c>
+      <c r="G187" s="0" t="inlineStr">
         <is>
           <t>The user with id '2' deleted the question with id '6639287' from the category with the id '405065'.</t>
         </is>
       </c>
-      <c r="H160" s="0" t="inlineStr">
+      <c r="H187" s="0" t="inlineStr">
         <is>
           <t>cli</t>
         </is>

--- a/Карнаухова Ольга Александровна/Математический анализ (Часть 2)/Журнал событий (id 1182).xlsx
+++ b/Карнаухова Ольга Александровна/Математический анализ (Часть 2)/Журнал событий (id 1182).xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I187"/>
+  <dimension ref="A1:I190"/>
   <sheetData>
     <row r="1" spans="1:9" customHeight="0">
       <c r="A1" s="0" t="inlineStr">
@@ -112,7 +112,7 @@
     <row r="2" spans="1:9" customHeight="0">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 13:28:29</t>
+          <t>18/10/26, 17:42:10</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -152,24 +152,24 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>94.183.167.62</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:9" customHeight="0">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 05:47:41</t>
+          <t>17/10/26, 16:26:48</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Мамай Егор Дмитриевич</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>Манкевич Максим Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -184,34 +184,39 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '208503' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '197096' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>10.3.224.130</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:9" customHeight="0">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 05:47:41</t>
+          <t>13/10/26, 13:28:31</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>Манкевич Максим Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -221,39 +226,44 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653269' for the user with id '208503' for the grade item with id '712649'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:9" customHeight="0">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 05:47:41</t>
+          <t>13/10/26, 13:28:29</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>Манкевич Максим Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -263,22 +273,27 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653249' for the user with id '208503' for the grade item with id '666279'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
@@ -310,12 +325,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653268' for the user with id '208503' for the grade item with id '524410'.</t>
+          <t>The user with id '0' unenrolled the user with id '208503' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -357,7 +372,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653267' for the user with id '208503' for the grade item with id '212337'.</t>
+          <t>The user with id '0' deleted the grade with id '61653269' for the user with id '208503' for the grade item with id '712649'.</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -399,7 +414,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653251' for the user with id '208503' for the grade item with id '202565'.</t>
+          <t>The user with id '0' deleted the grade with id '61653249' for the user with id '208503' for the grade item with id '666279'.</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -441,7 +456,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653250' for the user with id '208503' for the grade item with id '202489'.</t>
+          <t>The user with id '0' deleted the grade with id '61653268' for the user with id '208503' for the grade item with id '524410'.</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -483,7 +498,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653266' for the user with id '208503' for the grade item with id '193468'.</t>
+          <t>The user with id '0' deleted the grade with id '61653267' for the user with id '208503' for the grade item with id '212337'.</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -525,7 +540,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653265' for the user with id '208503' for the grade item with id '162883'.</t>
+          <t>The user with id '0' deleted the grade with id '61653251' for the user with id '208503' for the grade item with id '202565'.</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -567,7 +582,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653264' for the user with id '208503' for the grade item with id '162882'.</t>
+          <t>The user with id '0' deleted the grade with id '61653250' for the user with id '208503' for the grade item with id '202489'.</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -609,7 +624,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653248' for the user with id '208503' for the grade item with id '162872'.</t>
+          <t>The user with id '0' deleted the grade with id '61653266' for the user with id '208503' for the grade item with id '193468'.</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -651,7 +666,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653263' for the user with id '208503' for the grade item with id '13852'.</t>
+          <t>The user with id '0' deleted the grade with id '61653265' for the user with id '208503' for the grade item with id '162883'.</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -693,7 +708,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653262' for the user with id '208503' for the grade item with id '13850'.</t>
+          <t>The user with id '0' deleted the grade with id '61653264' for the user with id '208503' for the grade item with id '162882'.</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -735,7 +750,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653261' for the user with id '208503' for the grade item with id '13847'.</t>
+          <t>The user with id '0' deleted the grade with id '61653248' for the user with id '208503' for the grade item with id '162872'.</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -777,7 +792,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653260' for the user with id '208503' for the grade item with id '13845'.</t>
+          <t>The user with id '0' deleted the grade with id '61653263' for the user with id '208503' for the grade item with id '13852'.</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -819,7 +834,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653259' for the user with id '208503' for the grade item with id '13842'.</t>
+          <t>The user with id '0' deleted the grade with id '61653262' for the user with id '208503' for the grade item with id '13850'.</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -861,7 +876,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653258' for the user with id '208503' for the grade item with id '13839'.</t>
+          <t>The user with id '0' deleted the grade with id '61653261' for the user with id '208503' for the grade item with id '13847'.</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -903,7 +918,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653257' for the user with id '208503' for the grade item with id '13836'.</t>
+          <t>The user with id '0' deleted the grade with id '61653260' for the user with id '208503' for the grade item with id '13845'.</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -945,7 +960,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653256' for the user with id '208503' for the grade item with id '13834'.</t>
+          <t>The user with id '0' deleted the grade with id '61653259' for the user with id '208503' for the grade item with id '13842'.</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -987,7 +1002,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653255' for the user with id '208503' for the grade item with id '13830'.</t>
+          <t>The user with id '0' deleted the grade with id '61653258' for the user with id '208503' for the grade item with id '13839'.</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1029,7 +1044,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653254' for the user with id '208503' for the grade item with id '13827'.</t>
+          <t>The user with id '0' deleted the grade with id '61653257' for the user with id '208503' for the grade item with id '13836'.</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1071,7 +1086,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653253' for the user with id '208503' for the grade item with id '13823'.</t>
+          <t>The user with id '0' deleted the grade with id '61653256' for the user with id '208503' for the grade item with id '13834'.</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1113,7 +1128,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653252' for the user with id '208503' for the grade item with id '13821'.</t>
+          <t>The user with id '0' deleted the grade with id '61653255' for the user with id '208503' for the grade item with id '13830'.</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1150,12 +1165,12 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '208503'.</t>
+          <t>The user with id '0' deleted the grade with id '61653254' for the user with id '208503' for the grade item with id '13827'.</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1192,12 +1207,12 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '208503' from the group with id '107485'.</t>
+          <t>The user with id '0' deleted the grade with id '61653253' for the user with id '208503' for the grade item with id '13823'.</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1209,17 +1224,17 @@
     <row r="28" spans="1:9" customHeight="0">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:29:58</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -1229,44 +1244,39 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653252' for the user with id '208503' for the grade item with id '13821'.</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I28" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:9" customHeight="0">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:29:56</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -1276,44 +1286,39 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '208503'.</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I29" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:9" customHeight="0">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:18:39</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -1323,34 +1328,29 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' removed the user with id '208503' from the group with id '107485'.</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I30" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:9" customHeight="0">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:18:37</t>
+          <t>11/10/26, 09:29:58</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
@@ -1397,12 +1397,12 @@
     <row r="32" spans="1:9" customHeight="0">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>9/10/26, 20:27:09</t>
+          <t>11/10/26, 09:29:56</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>Сансызбай Нурбакыт -</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -1417,17 +1417,17 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222555' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -1437,19 +1437,19 @@
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>91.79.229.252</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:9" customHeight="0">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>7/10/26, 05:48:36</t>
+          <t>11/10/26, 09:18:39</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>Просмотрено описание курса</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>87.250.224.238</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:9" customHeight="0">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:19</t>
+          <t>11/10/26, 09:18:37</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:9" customHeight="0">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:14</t>
+          <t>9/10/26, 20:27:09</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Сансызбай Нурбакыт -</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -1558,17 +1558,17 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222555' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -1578,19 +1578,19 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>91.79.229.252</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:9" customHeight="0">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:07</t>
+          <t>7/10/26, 05:48:36</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Просмотрено описание курса</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -1625,24 +1625,24 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>87.250.224.238</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:9" customHeight="0">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>3/10/26, 05:43:06</t>
+          <t>4/10/26, 08:46:19</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Волков Даниил Феликсович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -1652,39 +1652,44 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '207098'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:9" customHeight="0">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>3/10/26, 05:43:06</t>
+          <t>4/10/26, 08:46:14</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Волков Даниил Феликсович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -1694,29 +1699,34 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '207098' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:9" customHeight="0">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:16</t>
+          <t>4/10/26, 08:46:07</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
@@ -1736,17 +1746,17 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -1763,17 +1773,17 @@
     <row r="40" spans="1:9" customHeight="0">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:12</t>
+          <t>3/10/26, 05:43:06</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Волков Даниил Феликсович</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -1783,44 +1793,39 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '207098'.</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I40" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:9" customHeight="0">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:04</t>
+          <t>3/10/26, 05:43:06</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Волков Даниил Феликсович</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -1835,29 +1840,24 @@
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' enrolled the user with id '207098' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I41" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:9" customHeight="0">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 09:51:46</t>
+          <t>29/09/26, 10:16:16</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
@@ -1877,17 +1877,17 @@
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -1904,7 +1904,7 @@
     <row r="43" spans="1:9" customHeight="0">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:31</t>
+          <t>29/09/26, 10:16:12</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="44" spans="1:9" customHeight="0">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:26</t>
+          <t>29/09/26, 10:16:04</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="45" spans="1:9" customHeight="0">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:18</t>
+          <t>29/09/26, 09:51:46</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
@@ -2045,12 +2045,12 @@
     <row r="46" spans="1:9" customHeight="0">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:38</t>
+          <t>27/09/26, 06:56:31</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -2060,22 +2060,22 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>Файл: Рабочая программа ВТ</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'resource' activity with course module id '2056915'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="I46" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.243</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:9" customHeight="0">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:33</t>
+          <t>27/09/26, 06:56:26</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -2107,22 +2107,22 @@
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>Страница: Список ссылок на источники материалов и/или правообладателей</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>Страница</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'page' activity with course module id '2056913'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -2132,19 +2132,19 @@
       </c>
       <c r="I47" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.243</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:9" customHeight="0">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:30</t>
+          <t>27/09/26, 06:56:18</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -2154,22 +2154,22 @@
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>Глоссарий: Глоссарий</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>Глоссарий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'glossary' activity with course module id '2056911'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -2179,14 +2179,14 @@
       </c>
       <c r="I48" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.243</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:9" customHeight="0">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:27</t>
+          <t>24/09/26, 17:00:38</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>Форум: Объявления</t>
+          <t>Файл: Рабочая программа ВТ</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
+          <t>The user with id '222925' viewed the 'resource' activity with course module id '2056915'.</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -2233,7 +2233,7 @@
     <row r="50" spans="1:9" customHeight="0">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:23</t>
+          <t>24/09/26, 17:00:33</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум группы КИ 21-05б</t>
+          <t>Страница: Список ссылок на источники материалов и/или правообладателей</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Страница</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1343322'.</t>
+          <t>The user with id '222925' viewed the 'page' activity with course module id '2056913'.</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -2280,7 +2280,7 @@
     <row r="51" spans="1:9" customHeight="0">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:11</t>
+          <t>24/09/26, 17:00:30</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум</t>
+          <t>Глоссарий: Глоссарий</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Глоссарий</t>
         </is>
       </c>
       <c r="F51" s="0" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
+          <t>The user with id '222925' viewed the 'glossary' activity with course module id '2056911'.</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="52" spans="1:9" customHeight="0">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:59:54</t>
+          <t>24/09/26, 17:00:27</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Объявления</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="53" spans="1:9" customHeight="0">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:56</t>
+          <t>24/09/26, 17:00:23</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>Форум: Объявления</t>
+          <t>Форум: Форум группы КИ 21-05б</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1343322'.</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="54" spans="1:9" customHeight="0">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:38</t>
+          <t>24/09/26, 17:00:11</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
@@ -2468,7 +2468,7 @@
     <row r="55" spans="1:9" customHeight="0">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:20</t>
+          <t>24/09/26, 16:59:54</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
@@ -2515,12 +2515,12 @@
     <row r="56" spans="1:9" customHeight="0">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:34</t>
+          <t>24/09/26, 16:49:56</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -2530,22 +2530,22 @@
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Объявления</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -2555,19 +2555,19 @@
       </c>
       <c r="I56" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:9" customHeight="0">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:29</t>
+          <t>24/09/26, 16:49:38</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -2577,22 +2577,22 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум</t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -2602,19 +2602,19 @@
       </c>
       <c r="I57" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:9" customHeight="0">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:22</t>
+          <t>24/09/26, 16:49:20</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -2649,19 +2649,19 @@
       </c>
       <c r="I58" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:9" customHeight="0">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 07:04:32</t>
+          <t>24/09/26, 12:05:34</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -2676,17 +2676,17 @@
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F59" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -2696,19 +2696,19 @@
       </c>
       <c r="I59" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.153</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:9" customHeight="0">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 22:40:18</t>
+          <t>24/09/26, 12:05:29</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>Тимофеева Алина Андреевна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222888' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -2743,14 +2743,14 @@
       </c>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>188.0.30.162</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:9" customHeight="0">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:56</t>
+          <t>24/09/26, 12:05:22</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
@@ -2770,17 +2770,17 @@
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -2797,12 +2797,12 @@
     <row r="62" spans="1:9" customHeight="0">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:28</t>
+          <t>24/09/26, 07:04:32</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -2837,19 +2837,19 @@
       </c>
       <c r="I62" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.153</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:9" customHeight="0">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:12</t>
+          <t>22/09/26, 22:40:18</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Тимофеева Алина Андреевна</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '222888' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="I63" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>188.0.30.162</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:9" customHeight="0">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:45:22</t>
+          <t>22/09/26, 17:50:56</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -2938,17 +2938,17 @@
     <row r="65" spans="1:9" customHeight="0">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:32</t>
+          <t>22/09/26, 17:50:28</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' assigned the role with id '4' to the user with id '168785'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -2978,24 +2978,24 @@
       </c>
       <c r="I65" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:9" customHeight="0">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:32</t>
+          <t>22/09/26, 17:50:12</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="F66" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' enrolled the user with id '168785' using the enrolment method 'manual' in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="I66" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:9" customHeight="0">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:02</t>
+          <t>22/09/26, 17:45:22</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="I67" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:9" customHeight="0">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:10:53</t>
+          <t>22/09/26, 15:11:32</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' viewed the course with id '1182'.</t>
+          <t>The user with id '32194' assigned the role with id '4' to the user with id '168785'.</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -3126,17 +3126,17 @@
     <row r="69" spans="1:9" customHeight="0">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>22/09/26, 15:11:32</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -3151,34 +3151,39 @@
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '218267' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '32194' enrolled the user with id '168785' using the enrolment method 'manual' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:9" customHeight="0">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>22/09/26, 15:11:02</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -3193,34 +3198,39 @@
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '218267' from the group with id '119772'.</t>
+          <t>The user with id '32194' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:9" customHeight="0">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>22/09/26, 15:10:53</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -3235,24 +3245,29 @@
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '218267'.</t>
+          <t>The user with id '32194' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:9" customHeight="0">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:26</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
@@ -3262,7 +3277,7 @@
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -3277,12 +3292,12 @@
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '209842'.</t>
+          <t>The user with id '0' unenrolled the user with id '218267' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -3294,7 +3309,7 @@
     <row r="73" spans="1:9" customHeight="0">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:26</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
@@ -3304,7 +3319,7 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -3319,12 +3334,12 @@
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '209842' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '0' removed the user with id '218267' from the group with id '119772'.</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -3336,7 +3351,7 @@
     <row r="74" spans="1:9" customHeight="0">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
@@ -3346,7 +3361,7 @@
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -3361,12 +3376,12 @@
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '209842' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '218267'.</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -3378,7 +3393,7 @@
     <row r="75" spans="1:9" customHeight="0">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:26</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
@@ -3403,12 +3418,12 @@
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971411' for the user with id '209842' for the grade item with id '712649'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '209842'.</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -3420,7 +3435,7 @@
     <row r="76" spans="1:9" customHeight="0">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:26</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
@@ -3445,12 +3460,12 @@
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971410' for the user with id '209842' for the grade item with id '666279'.</t>
+          <t>The user with id '0' enrolled the user with id '209842' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -3487,12 +3502,12 @@
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971409' for the user with id '209842' for the grade item with id '524410'.</t>
+          <t>The user with id '0' unenrolled the user with id '209842' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -3534,7 +3549,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971408' for the user with id '209842' for the grade item with id '212337'.</t>
+          <t>The user with id '0' deleted the grade with id '61971411' for the user with id '209842' for the grade item with id '712649'.</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -3576,7 +3591,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789133' for the user with id '209842' for the grade item with id '202565'.</t>
+          <t>The user with id '0' deleted the grade with id '61971410' for the user with id '209842' for the grade item with id '666279'.</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -3618,7 +3633,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789131' for the user with id '209842' for the grade item with id '202489'.</t>
+          <t>The user with id '0' deleted the grade with id '61971409' for the user with id '209842' for the grade item with id '524410'.</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -3660,7 +3675,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971407' for the user with id '209842' for the grade item with id '193468'.</t>
+          <t>The user with id '0' deleted the grade with id '61971408' for the user with id '209842' for the grade item with id '212337'.</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -3702,7 +3717,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971406' for the user with id '209842' for the grade item with id '162883'.</t>
+          <t>The user with id '0' deleted the grade with id '62789133' for the user with id '209842' for the grade item with id '202565'.</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -3744,7 +3759,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971405' for the user with id '209842' for the grade item with id '162882'.</t>
+          <t>The user with id '0' deleted the grade with id '62789131' for the user with id '209842' for the grade item with id '202489'.</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -3786,7 +3801,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789132' for the user with id '209842' for the grade item with id '162872'.</t>
+          <t>The user with id '0' deleted the grade with id '61971407' for the user with id '209842' for the grade item with id '193468'.</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -3828,7 +3843,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971404' for the user with id '209842' for the grade item with id '13852'.</t>
+          <t>The user with id '0' deleted the grade with id '61971406' for the user with id '209842' for the grade item with id '162883'.</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -3870,7 +3885,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971403' for the user with id '209842' for the grade item with id '13850'.</t>
+          <t>The user with id '0' deleted the grade with id '61971405' for the user with id '209842' for the grade item with id '162882'.</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -3912,7 +3927,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971402' for the user with id '209842' for the grade item with id '13847'.</t>
+          <t>The user with id '0' deleted the grade with id '62789132' for the user with id '209842' for the grade item with id '162872'.</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -3954,7 +3969,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971401' for the user with id '209842' for the grade item with id '13845'.</t>
+          <t>The user with id '0' deleted the grade with id '61971404' for the user with id '209842' for the grade item with id '13852'.</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -3996,7 +4011,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971400' for the user with id '209842' for the grade item with id '13842'.</t>
+          <t>The user with id '0' deleted the grade with id '61971403' for the user with id '209842' for the grade item with id '13850'.</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -4038,7 +4053,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971399' for the user with id '209842' for the grade item with id '13839'.</t>
+          <t>The user with id '0' deleted the grade with id '61971402' for the user with id '209842' for the grade item with id '13847'.</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -4080,7 +4095,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971398' for the user with id '209842' for the grade item with id '13836'.</t>
+          <t>The user with id '0' deleted the grade with id '61971401' for the user with id '209842' for the grade item with id '13845'.</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -4122,7 +4137,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971397' for the user with id '209842' for the grade item with id '13834'.</t>
+          <t>The user with id '0' deleted the grade with id '61971400' for the user with id '209842' for the grade item with id '13842'.</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -4164,7 +4179,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971396' for the user with id '209842' for the grade item with id '13830'.</t>
+          <t>The user with id '0' deleted the grade with id '61971399' for the user with id '209842' for the grade item with id '13839'.</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -4206,7 +4221,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971395' for the user with id '209842' for the grade item with id '13827'.</t>
+          <t>The user with id '0' deleted the grade with id '61971398' for the user with id '209842' for the grade item with id '13836'.</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -4248,7 +4263,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971393' for the user with id '209842' for the grade item with id '13823'.</t>
+          <t>The user with id '0' deleted the grade with id '61971397' for the user with id '209842' for the grade item with id '13834'.</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -4290,7 +4305,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971394' for the user with id '209842' for the grade item with id '13821'.</t>
+          <t>The user with id '0' deleted the grade with id '61971396' for the user with id '209842' for the grade item with id '13830'.</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -4327,12 +4342,12 @@
       </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '209842'.</t>
+          <t>The user with id '0' deleted the grade with id '61971395' for the user with id '209842' for the grade item with id '13827'.</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -4369,12 +4384,12 @@
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '209842' from the group with id '107484'.</t>
+          <t>The user with id '0' deleted the grade with id '61971393' for the user with id '209842' for the grade item with id '13823'.</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -4386,148 +4401,133 @@
     <row r="99" spans="1:9" customHeight="0">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:46</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 1</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '24773'.</t>
+          <t>The user with id '0' deleted the grade with id '61971394' for the user with id '209842' for the grade item with id '13821'.</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I99" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:9" customHeight="0">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:40</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 15</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '601904'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '209842'.</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I100" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:9" customHeight="0">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:30</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 5</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '440558'.</t>
+          <t>The user with id '0' removed the user with id '209842' from the group with id '107484'.</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I101" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:9" customHeight="0">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:26</t>
+          <t>17/09/26, 20:33:46</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
@@ -4542,22 +4542,22 @@
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 1</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '24773'.</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="103" spans="1:9" customHeight="0">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:21:20</t>
+          <t>17/09/26, 20:33:40</t>
         </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
@@ -4589,22 +4589,22 @@
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 15</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '601904'.</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="104" spans="1:9" customHeight="0">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:13</t>
+          <t>17/09/26, 20:33:30</t>
         </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум</t>
+          <t>Тест: Задачи к лекции 5</t>
         </is>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the 'forum' activity with course module id '24770'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '440558'.</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -4661,19 +4661,19 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>66.90.91.206</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:9" customHeight="0">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:07</t>
+          <t>17/09/26, 20:33:26</t>
         </is>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -4683,22 +4683,22 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум группы КИ 21-05б</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F105" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the 'forum' activity with course module id '1343322'.</t>
+          <t>The user with id '197464' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -4708,19 +4708,19 @@
       </c>
       <c r="I105" s="0" t="inlineStr">
         <is>
-          <t>66.90.91.206</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:9" customHeight="0">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:04</t>
+          <t>17/09/26, 20:21:20</t>
         </is>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -4755,108 +4755,118 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>66.90.91.206</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:9" customHeight="0">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>17/09/26, 00:35:13</t>
         </is>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум</t>
         </is>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F107" s="0" t="inlineStr">
         <is>
-          <t>Член группы добавлен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' added the user with id '176234' to the group with id '107484'.</t>
+          <t>The user with id '222427' viewed the 'forum' activity with course module id '24770'.</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:9" customHeight="0">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>17/09/26, 00:35:07</t>
         </is>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум группы КИ 21-05б</t>
         </is>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F108" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '176234'.</t>
+          <t>The user with id '222427' viewed the 'forum' activity with course module id '1343322'.</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:9" customHeight="0">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>17/09/26, 00:35:04</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -4871,34 +4881,39 @@
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '176234' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '222427' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:9" customHeight="0">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 07:24:42</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -4913,86 +4928,76 @@
       </c>
       <c r="F110" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Член группы добавлен</t>
         </is>
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' added the user with id '176234' to the group with id '107484'.</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I110" s="0" t="inlineStr">
-        <is>
-          <t>176.59.134.231</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:9" customHeight="0">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 01:47:10</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
-          <t>Файл: Вопросы к экзамену КИ23-03, КИ23-04, КИ23-05</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F111" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the 'resource' activity with course module id '548778'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '176234'.</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I111" s="0" t="inlineStr">
-        <is>
-          <t>176.116.166.86</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:9" customHeight="0">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 01:43:34</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -5007,39 +5012,34 @@
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' enrolled the user with id '176234' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I112" s="0" t="inlineStr">
-        <is>
-          <t>176.116.166.86</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:9" customHeight="0">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:27:38</t>
+          <t>16/09/26, 07:24:42</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the profile for the user with id '222427' in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -5069,44 +5069,44 @@
       </c>
       <c r="I113" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.59.134.231</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:9" customHeight="0">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:35</t>
+          <t>16/09/26, 01:47:10</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Вопросы к экзамену КИ23-03, КИ23-04, КИ23-05</t>
         </is>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F114" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the profile for the user with id '222375' in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the 'resource' activity with course module id '548778'.</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -5116,19 +5116,19 @@
       </c>
       <c r="I114" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.116.166.86</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:9" customHeight="0">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:16</t>
+          <t>16/09/26, 01:43:34</t>
         </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="F115" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="I115" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.116.166.86</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:9" customHeight="0">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:10</t>
+          <t>14/09/26, 14:27:38</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="F116" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the profile for the user with id '222427' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -5217,19 +5217,19 @@
     <row r="117" spans="1:9" customHeight="0">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 11:39:31</t>
+          <t>14/09/26, 14:26:35</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
           <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
-      <c r="C117" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
           <t>Курс: Математический анализ (Часть 2)</t>
@@ -5242,12 +5242,12 @@
       </c>
       <c r="F117" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the profile for the user with id '222375' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -5257,19 +5257,19 @@
       </c>
       <c r="I117" s="0" t="inlineStr">
         <is>
-          <t>176.59.145.192</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:9" customHeight="0">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>12/09/26, 16:36:10</t>
+          <t>14/09/26, 14:26:16</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>Моисеев Никита Андреевич</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="F118" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222376' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -5304,19 +5304,19 @@
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.144</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:9" customHeight="0">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>11/09/26, 20:05:31</t>
+          <t>14/09/26, 14:26:10</t>
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>Рагозина Виктория Викторовна</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198852' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -5351,14 +5351,14 @@
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.220</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:9" customHeight="0">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>11/09/26, 16:10:19</t>
+          <t>14/09/26, 11:39:31</t>
         </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
@@ -5398,24 +5398,24 @@
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>176.59.133.133</t>
+          <t>176.59.145.192</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:9" customHeight="0">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>12/09/26, 16:36:10</t>
         </is>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Моисеев Никита Андреевич</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -5430,34 +5430,39 @@
       </c>
       <c r="F121" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '217794' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '222376' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>188.0.28.144</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:9" customHeight="0">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>11/09/26, 20:05:31</t>
         </is>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Рагозина Виктория Викторовна</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -5472,34 +5477,39 @@
       </c>
       <c r="F122" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '217794' from the group with id '119772'.</t>
+          <t>The user with id '198852' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>188.0.28.220</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:9" customHeight="0">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>11/09/26, 16:10:19</t>
         </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -5514,81 +5524,81 @@
       </c>
       <c r="F123" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '217794'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>176.59.133.133</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:9" customHeight="0">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:41:03</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>Файл: Описание режима обучения</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the 'resource' activity with course module id '2056918'.</t>
+          <t>The user with id '0' unenrolled the user with id '217794' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I124" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:9" customHeight="0">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:58</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -5603,76 +5613,66 @@
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the course with id '1182'.</t>
+          <t>The user with id '0' removed the user with id '217794' from the group with id '119772'.</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I125" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:9" customHeight="0">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:50</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
-          <t>Отчет по тесту просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '217794'.</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I126" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:9" customHeight="0">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:39</t>
+          <t>9/09/26, 09:41:03</t>
         </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
@@ -5687,22 +5687,22 @@
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Файл: Описание режима обучения</t>
         </is>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
-          <t>Отчет по тесту просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
+          <t>The user with id '115989' viewed the 'resource' activity with course module id '2056918'.</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -5719,7 +5719,7 @@
     <row r="128" spans="1:9" customHeight="0">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:25</t>
+          <t>9/09/26, 09:40:58</t>
         </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
@@ -5734,22 +5734,22 @@
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the 'quiz' activity with course module id '24836'.</t>
+          <t>The user with id '115989' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -5766,12 +5766,12 @@
     <row r="129" spans="1:9" customHeight="0">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:48</t>
+          <t>9/09/26, 09:40:50</t>
         </is>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -5781,22 +5781,22 @@
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет по тесту просмотрен</t>
         </is>
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -5806,44 +5806,44 @@
       </c>
       <c r="I129" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:9" customHeight="0">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:43</t>
+          <t>9/09/26, 09:40:39</t>
         </is>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Отчет по тесту просмотрен</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' unenrolled the user with id '237748' using the enrolment method 'manual' from the course with id '1182'.</t>
+          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -5853,44 +5853,44 @@
       </c>
       <c r="I130" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:9" customHeight="0">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:43</t>
+          <t>9/09/26, 09:40:25</t>
         </is>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' unassigned the role with id '5' from the user with id '237748'.</t>
+          <t>The user with id '115989' viewed the 'quiz' activity with course module id '24836'.</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -5900,14 +5900,14 @@
       </c>
       <c r="I131" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:9" customHeight="0">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:28</t>
+          <t>7/09/26, 12:06:48</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="133" spans="1:9" customHeight="0">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:05:46</t>
+          <t>7/09/26, 12:06:43</t>
         </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="F133" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' removed the user with id '237748' from the group with id '118487'.</t>
+          <t>The user with id '20261' unenrolled the user with id '237748' using the enrolment method 'manual' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -6001,7 +6001,7 @@
     <row r="134" spans="1:9" customHeight="0">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:05:01</t>
+          <t>7/09/26, 12:06:43</t>
         </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t>Член группы добавлен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' added the user with id '237748' to the group with id '118487'.</t>
+          <t>The user with id '20261' unassigned the role with id '5' from the user with id '237748'.</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="135" spans="1:9" customHeight="0">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:57</t>
+          <t>7/09/26, 12:06:28</t>
         </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
@@ -6095,7 +6095,7 @@
     <row r="136" spans="1:9" customHeight="0">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:50</t>
+          <t>7/09/26, 12:05:46</t>
         </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' assigned the role with id '5' to the user with id '237748'.</t>
+          <t>The user with id '20261' removed the user with id '237748' from the group with id '118487'.</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -6142,7 +6142,7 @@
     <row r="137" spans="1:9" customHeight="0">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:50</t>
+          <t>7/09/26, 12:05:01</t>
         </is>
       </c>
       <c r="B137" s="0" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Член группы добавлен</t>
         </is>
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' enrolled the user with id '237748' using the enrolment method 'manual' in the course with id '1182'.</t>
+          <t>The user with id '20261' added the user with id '237748' to the group with id '118487'.</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -6189,7 +6189,7 @@
     <row r="138" spans="1:9" customHeight="0">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:02:43</t>
+          <t>7/09/26, 12:03:57</t>
         </is>
       </c>
       <c r="B138" s="0" t="inlineStr">
@@ -6236,7 +6236,7 @@
     <row r="139" spans="1:9" customHeight="0">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:02:39</t>
+          <t>7/09/26, 12:03:50</t>
         </is>
       </c>
       <c r="B139" s="0" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' assigned the role with id '5' to the user with id '237748'.</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -6283,17 +6283,17 @@
     <row r="140" spans="1:9" customHeight="0">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 11:42:02</t>
+          <t>7/09/26, 12:03:50</t>
         </is>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>Лаушкин Григорий Вадимович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="F140" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>The user with id '207594' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' enrolled the user with id '237748' using the enrolment method 'manual' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -6323,14 +6323,14 @@
       </c>
       <c r="I140" s="0" t="inlineStr">
         <is>
-          <t>10.30.102.26</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:9" customHeight="0">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t>3/09/26, 13:49:56</t>
+          <t>7/09/26, 12:02:43</t>
         </is>
       </c>
       <c r="B141" s="0" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="F141" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the section with id '12702'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -6377,7 +6377,7 @@
     <row r="142" spans="1:9" customHeight="0">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t>3/09/26, 13:49:45</t>
+          <t>7/09/26, 12:02:39</t>
         </is>
       </c>
       <c r="B142" s="0" t="inlineStr">
@@ -6424,12 +6424,12 @@
     <row r="143" spans="1:9" customHeight="0">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 18:03:03</t>
+          <t>7/09/26, 11:42:02</t>
         </is>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>Попова Виктория Максимовна</t>
+          <t>Лаушкин Григорий Вадимович</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 5</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E143" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F143" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221894' viewed the 'quiz' activity with course module id '440558'.</t>
+          <t>The user with id '207594' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -6464,19 +6464,19 @@
       </c>
       <c r="I143" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.152</t>
+          <t>10.30.102.26</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:9" customHeight="0">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 18:02:48</t>
+          <t>3/09/26, 13:49:56</t>
         </is>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>Попова Виктория Максимовна</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="F144" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Раздел просмотрен</t>
         </is>
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221894' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the section with id '12702'.</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -6511,19 +6511,19 @@
       </c>
       <c r="I144" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.152</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:9" customHeight="0">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 03:09:22</t>
+          <t>3/09/26, 13:49:45</t>
         </is>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>Ярусов Семён Александрович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222505' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -6558,44 +6558,44 @@
       </c>
       <c r="I145" s="0" t="inlineStr">
         <is>
-          <t>10.132.0.234</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:9" customHeight="0">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t>31/08/26, 17:07:41</t>
+          <t>2/09/26, 18:03:03</t>
         </is>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>Попова Виктория Максимовна</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 5</t>
         </is>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
-          <t>Отчет по пользователю</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F146" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Отчет по пользователю» просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>The user with id '217787' viewed the user report in the gradebook.</t>
+          <t>The user with id '221894' viewed the 'quiz' activity with course module id '440558'.</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -6605,19 +6605,19 @@
       </c>
       <c r="I146" s="0" t="inlineStr">
         <is>
-          <t>89.113.136.51</t>
+          <t>188.0.28.152</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:9" customHeight="0">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t>31/08/26, 17:07:36</t>
+          <t>2/09/26, 18:02:48</t>
         </is>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>Попова Виктория Максимовна</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>The user with id '217787' viewed the course with id '1182'.</t>
+          <t>The user with id '221894' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -6652,19 +6652,19 @@
       </c>
       <c r="I147" s="0" t="inlineStr">
         <is>
-          <t>89.113.136.51</t>
+          <t>188.0.28.152</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:9" customHeight="0">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 18:46:50</t>
+          <t>2/09/26, 03:09:22</t>
         </is>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>Николаев Виктор Анатольевич</t>
+          <t>Ярусов Семён Александрович</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221862' viewed the course with id '1182'.</t>
+          <t>The user with id '222505' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -6699,44 +6699,44 @@
       </c>
       <c r="I148" s="0" t="inlineStr">
         <is>
-          <t>176.59.130.167</t>
+          <t>10.132.0.234</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:9" customHeight="0">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:06:13</t>
+          <t>31/08/26, 17:07:41</t>
         </is>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Отчет по пользователю</t>
         </is>
       </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Отчет «Отчет по пользователю» просмотрен</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the 'resource' activity with course module id '24771'.</t>
+          <t>The user with id '217787' viewed the user report in the gradebook.</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -6746,19 +6746,19 @@
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>
-          <t>10.30.119.34</t>
+          <t>89.113.136.51</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:9" customHeight="0">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:05:42</t>
+          <t>31/08/26, 17:07:36</t>
         </is>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the course with id '1182'.</t>
+          <t>The user with id '217787' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -6793,24 +6793,24 @@
       </c>
       <c r="I150" s="0" t="inlineStr">
         <is>
-          <t>10.30.119.34</t>
+          <t>89.113.136.51</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:9" customHeight="0">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:05:39</t>
+          <t>30/08/26, 18:46:50</t>
         </is>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>Николаев Виктор Анатольевич</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>Тисецкая Анастасия Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="F151" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the profile for the user with id '196462' in the course with id '1182'.</t>
+          <t>The user with id '221862' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -6840,44 +6840,44 @@
       </c>
       <c r="I151" s="0" t="inlineStr">
         <is>
-          <t>10.30.119.34</t>
+          <t>176.59.130.167</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:9" customHeight="0">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:29</t>
+          <t>30/08/26, 01:06:13</t>
         </is>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 6</t>
+          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
         </is>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F152" s="0" t="inlineStr">
         <is>
-          <t>Завершенная попытка теста просмотрена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' has reviewed quiz attempt with id '9161794' by user with id '218896' for the quiz with course module id '24797'.</t>
+          <t>The user with id '198420' viewed the 'resource' activity with course module id '24771'.</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -6887,19 +6887,19 @@
       </c>
       <c r="I152" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:9" customHeight="0">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:23</t>
+          <t>30/08/26, 01:05:42</t>
         </is>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -6909,22 +6909,22 @@
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 6</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F153" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the 'quiz' activity with course module id '24797'.</t>
+          <t>The user with id '198420' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -6934,24 +6934,24 @@
       </c>
       <c r="I153" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:9" customHeight="0">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:11</t>
+          <t>30/08/26, 01:05:39</t>
         </is>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Тисецкая Анастасия Александровна</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F154" s="0" t="inlineStr">
         <is>
-          <t>Отчет по участнику курса просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the user report for the course with id '1182' for user with id '218896'.</t>
+          <t>The user with id '198420' viewed the profile for the user with id '196462' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -6981,14 +6981,14 @@
       </c>
       <c r="I154" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:9" customHeight="0">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:47:40</t>
+          <t>29/08/26, 21:48:29</t>
         </is>
       </c>
       <c r="B155" s="0" t="inlineStr">
@@ -6998,27 +6998,27 @@
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 6</t>
         </is>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F155" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Завершенная попытка теста просмотрена</t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the course with id '1182'.</t>
+          <t>The user with id '218896' has reviewed quiz attempt with id '9161794' by user with id '218896' for the quiz with course module id '24797'.</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -7035,12 +7035,12 @@
     <row r="156" spans="1:9" customHeight="0">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t>28/08/26, 14:05:02</t>
+          <t>29/08/26, 21:48:23</t>
         </is>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>Шишигин Никита Геннадьевич</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -7050,22 +7050,22 @@
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 6</t>
         </is>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F156" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>The user with id '220735' viewed the course with id '1182'.</t>
+          <t>The user with id '218896' viewed the 'quiz' activity with course module id '24797'.</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -7075,24 +7075,24 @@
       </c>
       <c r="I156" s="0" t="inlineStr">
         <is>
-          <t>91.132.20.254</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:9" customHeight="0">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t>26/08/26, 20:49:54</t>
+          <t>29/08/26, 21:48:11</t>
         </is>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="F157" s="0" t="inlineStr">
         <is>
-          <t>Просмотрено описание курса</t>
+          <t>Отчет по участнику курса просмотрен</t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
+          <t>The user with id '218896' viewed the user report for the course with id '1182' for user with id '218896'.</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -7122,19 +7122,19 @@
       </c>
       <c r="I157" s="0" t="inlineStr">
         <is>
-          <t>5.255.231.81</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:9" customHeight="0">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t>20/08/26, 23:30:20</t>
+          <t>29/08/26, 21:47:40</t>
         </is>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>Ооржак Анчы Вячеславович</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="F158" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222788' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '218896' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -7169,19 +7169,19 @@
       </c>
       <c r="I158" s="0" t="inlineStr">
         <is>
-          <t>185.193.199.22</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:9" customHeight="0">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t>20/08/26, 23:30:17</t>
+          <t>28/08/26, 14:05:02</t>
         </is>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>Ооржак Анчы Вячеславович</t>
+          <t>Шишигин Никита Геннадьевич</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222788' viewed the course with id '1182'.</t>
+          <t>The user with id '220735' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -7216,19 +7216,19 @@
       </c>
       <c r="I159" s="0" t="inlineStr">
         <is>
-          <t>185.193.199.22</t>
+          <t>91.132.20.254</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:9" customHeight="0">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:26</t>
+          <t>26/08/26, 20:49:54</t>
         </is>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="F160" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Просмотрено описание курса</t>
         </is>
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -7263,19 +7263,19 @@
       </c>
       <c r="I160" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>5.255.231.81</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:9" customHeight="0">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:23</t>
+          <t>20/08/26, 23:30:20</t>
         </is>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Ооржак Анчы Вячеславович</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="F161" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '222788' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -7310,19 +7310,19 @@
       </c>
       <c r="I161" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>185.193.199.22</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:9" customHeight="0">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:22</t>
+          <t>20/08/26, 23:30:17</t>
         </is>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Ооржак Анчы Вячеславович</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="F162" s="0" t="inlineStr">
         <is>
-          <t>Курс обновлен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' updated the course with id '1182'.</t>
+          <t>The user with id '222788' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="I162" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>185.193.199.22</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:9" customHeight="0">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:40</t>
+          <t>18/08/26, 12:27:26</t>
         </is>
       </c>
       <c r="B163" s="0" t="inlineStr">
@@ -7411,7 +7411,7 @@
     <row r="164" spans="1:9" customHeight="0">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:20</t>
+          <t>18/08/26, 12:27:23</t>
         </is>
       </c>
       <c r="B164" s="0" t="inlineStr">
@@ -7458,7 +7458,7 @@
     <row r="165" spans="1:9" customHeight="0">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:12</t>
+          <t>18/08/26, 12:27:22</t>
         </is>
       </c>
       <c r="B165" s="0" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="F165" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Курс обновлен</t>
         </is>
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' updated the course with id '1182'.</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -7505,7 +7505,7 @@
     <row r="166" spans="1:9" customHeight="0">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:12</t>
+          <t>18/08/26, 12:26:40</t>
         </is>
       </c>
       <c r="B166" s="0" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="F166" s="0" t="inlineStr">
         <is>
-          <t>Курс обновлен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' updated the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -7552,7 +7552,7 @@
     <row r="167" spans="1:9" customHeight="0">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:55</t>
+          <t>18/08/26, 12:26:20</t>
         </is>
       </c>
       <c r="B167" s="0" t="inlineStr">
@@ -7599,7 +7599,7 @@
     <row r="168" spans="1:9" customHeight="0">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:17</t>
+          <t>18/08/26, 12:26:12</t>
         </is>
       </c>
       <c r="B168" s="0" t="inlineStr">
@@ -7646,7 +7646,7 @@
     <row r="169" spans="1:9" customHeight="0">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:03</t>
+          <t>18/08/26, 12:26:12</t>
         </is>
       </c>
       <c r="B169" s="0" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="F169" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Курс обновлен</t>
         </is>
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' updated the course with id '1182'.</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -7693,7 +7693,7 @@
     <row r="170" spans="1:9" customHeight="0">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:20:38</t>
+          <t>18/08/26, 12:21:55</t>
         </is>
       </c>
       <c r="B170" s="0" t="inlineStr">
@@ -7740,12 +7740,12 @@
     <row r="171" spans="1:9" customHeight="0">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t>17/08/26, 13:54:23</t>
+          <t>18/08/26, 12:21:17</t>
         </is>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>Гудин Степан Денисович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -7755,22 +7755,22 @@
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 2</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F171" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222257' viewed the 'quiz' activity with course module id '24778'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -7780,19 +7780,19 @@
       </c>
       <c r="I171" s="0" t="inlineStr">
         <is>
-          <t>10.28.71.178</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:9" customHeight="0">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t>17/08/26, 13:54:13</t>
+          <t>18/08/26, 12:21:03</t>
         </is>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>Гудин Степан Денисович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222257' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -7827,19 +7827,19 @@
       </c>
       <c r="I172" s="0" t="inlineStr">
         <is>
-          <t>10.28.71.178</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:9" customHeight="0">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 19:11:54</t>
+          <t>18/08/26, 12:20:38</t>
         </is>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -7874,19 +7874,19 @@
       </c>
       <c r="I173" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:9" customHeight="0">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 17:28:04</t>
+          <t>17/08/26, 13:54:23</t>
         </is>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Гудин Степан Денисович</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
+          <t>Тест: Задачи к лекции 2</t>
         </is>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F174" s="0" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'resource' activity with course module id '24771'.</t>
+          <t>The user with id '222257' viewed the 'quiz' activity with course module id '24778'.</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -7921,19 +7921,19 @@
       </c>
       <c r="I174" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>10.28.71.178</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:9" customHeight="0">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 17:23:59</t>
+          <t>17/08/26, 13:54:13</t>
         </is>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Гудин Степан Денисович</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '222257' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -7968,19 +7968,19 @@
       </c>
       <c r="I175" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>10.28.71.178</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:9" customHeight="0">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:25</t>
+          <t>16/08/26, 19:11:54</t>
         </is>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="F176" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '171426'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -8015,19 +8015,19 @@
       </c>
       <c r="I176" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>176.49.89.56</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:9" customHeight="0">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:21</t>
+          <t>16/08/26, 17:28:04</t>
         </is>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D177" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 8. Формула Грина. Независимость криволинейного интеграла 2-го рода от пути интегрирования</t>
+          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
         </is>
       </c>
       <c r="E177" s="0" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '440562'.</t>
+          <t>The user with id '222925' viewed the 'resource' activity with course module id '24771'.</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -8062,19 +8062,19 @@
       </c>
       <c r="I177" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>176.49.89.56</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:9" customHeight="0">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:09</t>
+          <t>16/08/26, 17:23:59</t>
         </is>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="F178" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12711'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -8109,14 +8109,14 @@
       </c>
       <c r="I178" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>176.49.89.56</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:9" customHeight="0">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:05</t>
+          <t>16/08/26, 00:10:25</t>
         </is>
       </c>
       <c r="B179" s="0" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12714'.</t>
+          <t>The user with id '223842' viewed the section with id '171426'.</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -8163,7 +8163,7 @@
     <row r="180" spans="1:9" customHeight="0">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:01</t>
+          <t>16/08/26, 00:10:21</t>
         </is>
       </c>
       <c r="B180" s="0" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 16. Функциональные ряды. Основные понятия. Степенные ряды. Свойства степенных рядов. Разложение функции в степенные ряды. Ряд Тейлора. Ряд Маклорена</t>
+          <t>Файл: Лекция 8. Формула Грина. Независимость криволинейного интеграла 2-го рода от пути интегрирования</t>
         </is>
       </c>
       <c r="E180" s="0" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '440645'.</t>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '440562'.</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -8210,7 +8210,7 @@
     <row r="181" spans="1:9" customHeight="0">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:56</t>
+          <t>16/08/26, 00:10:09</t>
         </is>
       </c>
       <c r="B181" s="0" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12706'.</t>
+          <t>The user with id '223842' viewed the section with id '12711'.</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="182" spans="1:9" customHeight="0">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:47</t>
+          <t>16/08/26, 00:10:05</t>
         </is>
       </c>
       <c r="B182" s="0" t="inlineStr">
@@ -8272,22 +8272,22 @@
       </c>
       <c r="D182" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 2.  Дифференцируемость и полный дифференциал ФНП. Дифференциалы высших порядков. Производная сложной функции. Производная неявной функции. Производная по направлению. Градиент</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E182" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F182" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Раздел просмотрен</t>
         </is>
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '24776'.</t>
+          <t>The user with id '223842' viewed the section with id '12714'.</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -8304,7 +8304,7 @@
     <row r="183" spans="1:9" customHeight="0">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:40</t>
+          <t>16/08/26, 00:10:01</t>
         </is>
       </c>
       <c r="B183" s="0" t="inlineStr">
@@ -8319,22 +8319,22 @@
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Лекция 16. Функциональные ряды. Основные понятия. Степенные ряды. Свойства степенных рядов. Разложение функции в степенные ряды. Ряд Тейлора. Ряд Маклорена</t>
         </is>
       </c>
       <c r="E183" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F183" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the course with id '1182'.</t>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '440645'.</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -8351,12 +8351,12 @@
     <row r="184" spans="1:9" customHeight="0">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t>31/07/26, 13:15:41</t>
+          <t>16/08/26, 00:09:56</t>
         </is>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>Войченко Антон Дмитриевич</t>
+          <t>Марков Сергей Денисович</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -8376,12 +8376,12 @@
       </c>
       <c r="F184" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Раздел просмотрен</t>
         </is>
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218660' viewed the course with id '1182'.</t>
+          <t>The user with id '223842' viewed the section with id '12706'.</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -8391,19 +8391,19 @@
       </c>
       <c r="I184" s="0" t="inlineStr">
         <is>
-          <t>193.8.74.6</t>
+          <t>62.68.153.224</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:9" customHeight="0">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t>16/07/26, 16:23:26</t>
+          <t>16/08/26, 00:09:47</t>
         </is>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>Администратор системы</t>
+          <t>Марков Сергей Денисович</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -8413,39 +8413,44 @@
       </c>
       <c r="D185" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Файл: Лекция 2.  Дифференцируемость и полный дифференциал ФНП. Дифференциалы высших порядков. Производная сложной функции. Производная неявной функции. Производная по направлению. Градиент</t>
         </is>
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F185" s="0" t="inlineStr">
         <is>
-          <t>Вопрос удален</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>The user with id '2' deleted the question with id '103599' from the category with the id '7395'.</t>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '24776'.</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I185" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:9" customHeight="0">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t>16/07/26, 16:23:26</t>
+          <t>16/08/26, 00:09:40</t>
         </is>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>Администратор системы</t>
+          <t>Марков Сергей Денисович</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -8455,7 +8460,7 @@
       </c>
       <c r="D186" s="0" t="inlineStr">
         <is>
-          <t>Банк вопросов: Математический анализ (Часть 2) - общий банк вопросов</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E186" s="0" t="inlineStr">
@@ -8465,57 +8470,193 @@
       </c>
       <c r="F186" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса создан</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>The user with id '2' created the 'qbank' activity with course module id '2058071'.</t>
+          <t>The user with id '223842' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I186" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:9" customHeight="0">
       <c r="A187" s="0" t="inlineStr">
         <is>
+          <t>31/07/26, 13:15:41</t>
+        </is>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t>Войченко Антон Дмитриевич</t>
+        </is>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F187" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G187" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '218660' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H187" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I187" s="0" t="inlineStr">
+        <is>
+          <t>193.8.74.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" spans="1:9" customHeight="0">
+      <c r="A188" s="0" t="inlineStr">
+        <is>
           <t>16/07/26, 16:23:26</t>
         </is>
       </c>
-      <c r="B187" s="0" t="inlineStr">
+      <c r="B188" s="0" t="inlineStr">
         <is>
           <t>Администратор системы</t>
         </is>
       </c>
-      <c r="C187" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D187" s="0" t="inlineStr">
-        <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
-        </is>
-      </c>
-      <c r="E187" s="0" t="inlineStr">
-        <is>
-          <t>Система</t>
-        </is>
-      </c>
-      <c r="F187" s="0" t="inlineStr">
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t>Тест: Задачи к лекции 14</t>
+        </is>
+      </c>
+      <c r="E188" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F188" s="0" t="inlineStr">
         <is>
           <t>Вопрос удален</t>
         </is>
       </c>
-      <c r="G187" s="0" t="inlineStr">
+      <c r="G188" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '2' deleted the question with id '103599' from the category with the id '7395'.</t>
+        </is>
+      </c>
+      <c r="H188" s="0" t="inlineStr">
+        <is>
+          <t>cli</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" spans="1:9" customHeight="0">
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t>16/07/26, 16:23:26</t>
+        </is>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>Администратор системы</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t>Банк вопросов: Математический анализ (Часть 2) - общий банк вопросов</t>
+        </is>
+      </c>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F189" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса создан</t>
+        </is>
+      </c>
+      <c r="G189" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '2' created the 'qbank' activity with course module id '2058071'.</t>
+        </is>
+      </c>
+      <c r="H189" s="0" t="inlineStr">
+        <is>
+          <t>cli</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" spans="1:9" customHeight="0">
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t>16/07/26, 16:23:26</t>
+        </is>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>Администратор системы</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F190" s="0" t="inlineStr">
+        <is>
+          <t>Вопрос удален</t>
+        </is>
+      </c>
+      <c r="G190" s="0" t="inlineStr">
         <is>
           <t>The user with id '2' deleted the question with id '6639287' from the category with the id '405065'.</t>
         </is>
       </c>
-      <c r="H187" s="0" t="inlineStr">
+      <c r="H190" s="0" t="inlineStr">
         <is>
           <t>cli</t>
         </is>

--- a/Карнаухова Ольга Александровна/Математический анализ (Часть 2)/Журнал событий (id 1182).xlsx
+++ b/Карнаухова Ольга Александровна/Математический анализ (Часть 2)/Журнал событий (id 1182).xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I193"/>
   <sheetData>
     <row r="1" spans="1:9" customHeight="0">
       <c r="A1" s="0" t="inlineStr">
@@ -112,7 +112,7 @@
     <row r="2" spans="1:9" customHeight="0">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>18/10/26, 17:42:10</t>
+          <t>26/10/26, 11:15:31</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="3" spans="1:9" customHeight="0">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>17/10/26, 16:26:48</t>
+          <t>24/10/26, 11:10:53</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Мамай Егор Дмитриевич</t>
+          <t>Киселев Илья Владиславович</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197096' viewed the course with id '1182'.</t>
+          <t>The user with id '207721' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -199,14 +199,14 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>10.3.224.130</t>
+          <t>171.33.254.185</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:9" customHeight="0">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 13:28:31</t>
+          <t>18/10/26, 17:42:15</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
@@ -246,14 +246,14 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>94.183.167.62</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:9" customHeight="0">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 13:28:29</t>
+          <t>18/10/26, 17:42:10</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
@@ -293,24 +293,24 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>94.183.167.62</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:9" customHeight="0">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 05:47:41</t>
+          <t>17/10/26, 16:26:48</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Мамай Егор Дмитриевич</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>Манкевич Максим Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -325,34 +325,39 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '208503' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '197096' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>10.3.224.130</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:9" customHeight="0">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 05:47:41</t>
+          <t>13/10/26, 13:28:31</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>Манкевич Максим Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -362,39 +367,44 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653269' for the user with id '208503' for the grade item with id '712649'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:9" customHeight="0">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>13/10/26, 05:47:41</t>
+          <t>13/10/26, 13:28:29</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Манкевич Максим Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -404,22 +414,27 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653249' for the user with id '208503' for the grade item with id '666279'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
@@ -451,12 +466,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653268' for the user with id '208503' for the grade item with id '524410'.</t>
+          <t>The user with id '0' unenrolled the user with id '208503' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -498,7 +513,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653267' for the user with id '208503' for the grade item with id '212337'.</t>
+          <t>The user with id '0' deleted the grade with id '61653269' for the user with id '208503' for the grade item with id '712649'.</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -540,7 +555,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653251' for the user with id '208503' for the grade item with id '202565'.</t>
+          <t>The user with id '0' deleted the grade with id '61653249' for the user with id '208503' for the grade item with id '666279'.</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -582,7 +597,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653250' for the user with id '208503' for the grade item with id '202489'.</t>
+          <t>The user with id '0' deleted the grade with id '61653268' for the user with id '208503' for the grade item with id '524410'.</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -624,7 +639,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653266' for the user with id '208503' for the grade item with id '193468'.</t>
+          <t>The user with id '0' deleted the grade with id '61653267' for the user with id '208503' for the grade item with id '212337'.</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -666,7 +681,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653265' for the user with id '208503' for the grade item with id '162883'.</t>
+          <t>The user with id '0' deleted the grade with id '61653251' for the user with id '208503' for the grade item with id '202565'.</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -708,7 +723,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653264' for the user with id '208503' for the grade item with id '162882'.</t>
+          <t>The user with id '0' deleted the grade with id '61653250' for the user with id '208503' for the grade item with id '202489'.</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -750,7 +765,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653248' for the user with id '208503' for the grade item with id '162872'.</t>
+          <t>The user with id '0' deleted the grade with id '61653266' for the user with id '208503' for the grade item with id '193468'.</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -792,7 +807,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653263' for the user with id '208503' for the grade item with id '13852'.</t>
+          <t>The user with id '0' deleted the grade with id '61653265' for the user with id '208503' for the grade item with id '162883'.</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -834,7 +849,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653262' for the user with id '208503' for the grade item with id '13850'.</t>
+          <t>The user with id '0' deleted the grade with id '61653264' for the user with id '208503' for the grade item with id '162882'.</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -876,7 +891,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653261' for the user with id '208503' for the grade item with id '13847'.</t>
+          <t>The user with id '0' deleted the grade with id '61653248' for the user with id '208503' for the grade item with id '162872'.</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -918,7 +933,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653260' for the user with id '208503' for the grade item with id '13845'.</t>
+          <t>The user with id '0' deleted the grade with id '61653263' for the user with id '208503' for the grade item with id '13852'.</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -960,7 +975,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653259' for the user with id '208503' for the grade item with id '13842'.</t>
+          <t>The user with id '0' deleted the grade with id '61653262' for the user with id '208503' for the grade item with id '13850'.</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1002,7 +1017,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653258' for the user with id '208503' for the grade item with id '13839'.</t>
+          <t>The user with id '0' deleted the grade with id '61653261' for the user with id '208503' for the grade item with id '13847'.</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1044,7 +1059,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653257' for the user with id '208503' for the grade item with id '13836'.</t>
+          <t>The user with id '0' deleted the grade with id '61653260' for the user with id '208503' for the grade item with id '13845'.</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1086,7 +1101,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653256' for the user with id '208503' for the grade item with id '13834'.</t>
+          <t>The user with id '0' deleted the grade with id '61653259' for the user with id '208503' for the grade item with id '13842'.</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1128,7 +1143,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653255' for the user with id '208503' for the grade item with id '13830'.</t>
+          <t>The user with id '0' deleted the grade with id '61653258' for the user with id '208503' for the grade item with id '13839'.</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1170,7 +1185,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653254' for the user with id '208503' for the grade item with id '13827'.</t>
+          <t>The user with id '0' deleted the grade with id '61653257' for the user with id '208503' for the grade item with id '13836'.</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1212,7 +1227,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653253' for the user with id '208503' for the grade item with id '13823'.</t>
+          <t>The user with id '0' deleted the grade with id '61653256' for the user with id '208503' for the grade item with id '13834'.</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1254,7 +1269,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61653252' for the user with id '208503' for the grade item with id '13821'.</t>
+          <t>The user with id '0' deleted the grade with id '61653255' for the user with id '208503' for the grade item with id '13830'.</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1291,12 +1306,12 @@
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '208503'.</t>
+          <t>The user with id '0' deleted the grade with id '61653254' for the user with id '208503' for the grade item with id '13827'.</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1333,12 +1348,12 @@
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '208503' from the group with id '107485'.</t>
+          <t>The user with id '0' deleted the grade with id '61653253' for the user with id '208503' for the grade item with id '13823'.</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -1350,17 +1365,17 @@
     <row r="31" spans="1:9" customHeight="0">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:29:58</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -1370,44 +1385,39 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' deleted the grade with id '61653252' for the user with id '208503' for the grade item with id '13821'.</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I31" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:9" customHeight="0">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:29:56</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -1417,44 +1427,39 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '208503'.</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I32" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:9" customHeight="0">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:18:39</t>
+          <t>13/10/26, 05:47:41</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Манкевич Максим Евгеньевич</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -1464,34 +1469,29 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' removed the user with id '208503' from the group with id '107485'.</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I33" s="0" t="inlineStr">
-        <is>
-          <t>94.183.167.62</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:9" customHeight="0">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>11/10/26, 09:18:37</t>
+          <t>11/10/26, 09:29:58</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="35" spans="1:9" customHeight="0">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>9/10/26, 20:27:09</t>
+          <t>11/10/26, 09:29:56</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>Сансызбай Нурбакыт -</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -1558,17 +1558,17 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222555' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -1578,19 +1578,19 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>91.79.229.252</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:9" customHeight="0">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>7/10/26, 05:48:36</t>
+          <t>11/10/26, 09:18:39</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t>Просмотрено описание курса</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -1625,14 +1625,14 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>87.250.224.238</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:9" customHeight="0">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:19</t>
+          <t>11/10/26, 09:18:37</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
@@ -1672,19 +1672,19 @@
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>94.183.167.62</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:9" customHeight="0">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:14</t>
+          <t>9/10/26, 20:27:09</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Сансызбай Нурбакыт -</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -1699,17 +1699,17 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222555' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -1719,19 +1719,19 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>91.79.229.252</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:9" customHeight="0">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>4/10/26, 08:46:07</t>
+          <t>7/10/26, 05:48:36</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Просмотрено описание курса</t>
         </is>
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -1766,24 +1766,24 @@
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>87.250.224.238</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:9" customHeight="0">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>3/10/26, 05:43:06</t>
+          <t>4/10/26, 08:46:19</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Волков Даниил Феликсович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -1793,39 +1793,44 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '207098'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:9" customHeight="0">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>3/10/26, 05:43:06</t>
+          <t>4/10/26, 08:46:14</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Волков Даниил Феликсович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -1835,29 +1840,34 @@
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '207098' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:9" customHeight="0">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:16</t>
+          <t>4/10/26, 08:46:07</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
@@ -1877,17 +1887,17 @@
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -1904,17 +1914,17 @@
     <row r="43" spans="1:9" customHeight="0">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:12</t>
+          <t>3/10/26, 05:43:06</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Волков Даниил Феликсович</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -1924,44 +1934,39 @@
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '207098'.</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I43" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:9" customHeight="0">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 10:16:04</t>
+          <t>3/10/26, 05:43:06</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Волков Даниил Феликсович</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -1976,29 +1981,24 @@
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '0' enrolled the user with id '207098' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I44" s="0" t="inlineStr">
-        <is>
-          <t>109.226.212.133</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:9" customHeight="0">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>29/09/26, 09:51:46</t>
+          <t>29/09/26, 10:16:16</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="46" spans="1:9" customHeight="0">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:31</t>
+          <t>29/09/26, 10:16:12</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="47" spans="1:9" customHeight="0">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:26</t>
+          <t>29/09/26, 10:16:04</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="48" spans="1:9" customHeight="0">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>27/09/26, 06:56:18</t>
+          <t>29/09/26, 09:51:46</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
@@ -2186,12 +2186,12 @@
     <row r="49" spans="1:9" customHeight="0">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:38</t>
+          <t>27/09/26, 06:56:31</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -2201,22 +2201,22 @@
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>Файл: Рабочая программа ВТ</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'resource' activity with course module id '2056915'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -2226,19 +2226,19 @@
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.243</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:9" customHeight="0">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:33</t>
+          <t>27/09/26, 06:56:26</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -2248,22 +2248,22 @@
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>Страница: Список ссылок на источники материалов и/или правообладателей</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>Страница</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'page' activity with course module id '2056913'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -2273,19 +2273,19 @@
       </c>
       <c r="I50" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.243</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:9" customHeight="0">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:30</t>
+          <t>27/09/26, 06:56:18</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -2295,22 +2295,22 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>Глоссарий: Глоссарий</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>Глоссарий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'glossary' activity with course module id '2056911'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -2320,14 +2320,14 @@
       </c>
       <c r="I51" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.243</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:9" customHeight="0">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:27</t>
+          <t>24/09/26, 17:00:38</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>Форум: Объявления</t>
+          <t>Файл: Рабочая программа ВТ</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
+          <t>The user with id '222925' viewed the 'resource' activity with course module id '2056915'.</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="53" spans="1:9" customHeight="0">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:23</t>
+          <t>24/09/26, 17:00:33</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум группы КИ 21-05б</t>
+          <t>Страница: Список ссылок на источники материалов и/или правообладателей</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Страница</t>
         </is>
       </c>
       <c r="F53" s="0" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1343322'.</t>
+          <t>The user with id '222925' viewed the 'page' activity with course module id '2056913'.</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="54" spans="1:9" customHeight="0">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 17:00:11</t>
+          <t>24/09/26, 17:00:30</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум</t>
+          <t>Глоссарий: Глоссарий</t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Глоссарий</t>
         </is>
       </c>
       <c r="F54" s="0" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
+          <t>The user with id '222925' viewed the 'glossary' activity with course module id '2056911'.</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -2468,7 +2468,7 @@
     <row r="55" spans="1:9" customHeight="0">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:59:54</t>
+          <t>24/09/26, 17:00:27</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
@@ -2483,22 +2483,22 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Объявления</t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -2515,7 +2515,7 @@
     <row r="56" spans="1:9" customHeight="0">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:56</t>
+          <t>24/09/26, 17:00:23</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>Форум: Объявления</t>
+          <t>Форум: Форум группы КИ 21-05б</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1343322'.</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="57" spans="1:9" customHeight="0">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:38</t>
+          <t>24/09/26, 17:00:11</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="58" spans="1:9" customHeight="0">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 16:49:20</t>
+          <t>24/09/26, 16:59:54</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
@@ -2656,12 +2656,12 @@
     <row r="59" spans="1:9" customHeight="0">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:34</t>
+          <t>24/09/26, 16:49:56</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -2671,22 +2671,22 @@
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Объявления</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F59" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '1390115'.</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -2696,19 +2696,19 @@
       </c>
       <c r="I59" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:9" customHeight="0">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:29</t>
+          <t>24/09/26, 16:49:38</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум</t>
         </is>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the 'forum' activity with course module id '24770'.</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -2743,19 +2743,19 @@
       </c>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:9" customHeight="0">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 12:05:22</t>
+          <t>24/09/26, 16:49:20</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -2790,19 +2790,19 @@
       </c>
       <c r="I61" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.243</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:9" customHeight="0">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t>24/09/26, 07:04:32</t>
+          <t>24/09/26, 12:05:34</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -2837,19 +2837,19 @@
       </c>
       <c r="I62" s="0" t="inlineStr">
         <is>
-          <t>82.146.19.153</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:9" customHeight="0">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 22:40:18</t>
+          <t>24/09/26, 12:05:29</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>Тимофеева Алина Андреевна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222888' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="I63" s="0" t="inlineStr">
         <is>
-          <t>188.0.30.162</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:9" customHeight="0">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:56</t>
+          <t>24/09/26, 12:05:22</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -2938,12 +2938,12 @@
     <row r="65" spans="1:9" customHeight="0">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:28</t>
+          <t>24/09/26, 07:04:32</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>Журнал событий</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Журнал событий» просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -2978,19 +2978,19 @@
       </c>
       <c r="I65" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>82.146.19.153</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:9" customHeight="0">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:50:12</t>
+          <t>22/09/26, 22:40:18</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>Тимофеева Алина Андреевна</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '222888' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -3025,14 +3025,14 @@
       </c>
       <c r="I66" s="0" t="inlineStr">
         <is>
-          <t>109.226.212.133</t>
+          <t>188.0.30.162</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:9" customHeight="0">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 17:45:22</t>
+          <t>22/09/26, 17:50:56</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>The user with id '168785' viewed the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -3079,17 +3079,17 @@
     <row r="68" spans="1:9" customHeight="0">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:32</t>
+          <t>22/09/26, 17:50:28</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -3099,17 +3099,17 @@
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Журнал событий</t>
         </is>
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Отчет «Журнал событий» просмотрен</t>
         </is>
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' assigned the role with id '4' to the user with id '168785'.</t>
+          <t>The user with id '168785' viewed the log report for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -3119,24 +3119,24 @@
       </c>
       <c r="I68" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:9" customHeight="0">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:32</t>
+          <t>22/09/26, 17:50:12</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Батуро Евгений Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' enrolled the user with id '168785' using the enrolment method 'manual' in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -3166,19 +3166,19 @@
       </c>
       <c r="I69" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:9" customHeight="0">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:11:02</t>
+          <t>22/09/26, 17:45:22</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>Карнаухова Ольга Александровна</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '168785' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -3213,14 +3213,14 @@
       </c>
       <c r="I70" s="0" t="inlineStr">
         <is>
-          <t>176.116.179.187</t>
+          <t>109.226.212.133</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:9" customHeight="0">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t>22/09/26, 15:10:53</t>
+          <t>22/09/26, 15:11:32</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>The user with id '32194' viewed the course with id '1182'.</t>
+          <t>The user with id '32194' assigned the role with id '4' to the user with id '168785'.</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -3267,17 +3267,17 @@
     <row r="72" spans="1:9" customHeight="0">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>22/09/26, 15:11:32</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>Батуро Евгений Александрович</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -3292,34 +3292,39 @@
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '218267' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '32194' enrolled the user with id '168785' using the enrolment method 'manual' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:9" customHeight="0">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>22/09/26, 15:11:02</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -3334,34 +3339,39 @@
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '218267' from the group with id '119772'.</t>
+          <t>The user with id '32194' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:9" customHeight="0">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:28</t>
+          <t>22/09/26, 15:10:53</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Карнаухова Ольга Александровна</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Миллер Александр Алексеевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -3376,24 +3386,29 @@
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '218267'.</t>
+          <t>The user with id '32194' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>176.116.179.187</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:9" customHeight="0">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:26</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
@@ -3403,7 +3418,7 @@
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -3418,12 +3433,12 @@
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '209842'.</t>
+          <t>The user with id '0' unenrolled the user with id '218267' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -3435,7 +3450,7 @@
     <row r="76" spans="1:9" customHeight="0">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:26</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
@@ -3445,7 +3460,7 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -3460,12 +3475,12 @@
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '209842' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '0' removed the user with id '218267' from the group with id '119772'.</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -3477,7 +3492,7 @@
     <row r="77" spans="1:9" customHeight="0">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:28</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
@@ -3487,7 +3502,7 @@
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Емельянов Владимир Александрович</t>
+          <t>Миллер Александр Алексеевич</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -3502,12 +3517,12 @@
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '209842' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '218267'.</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -3519,7 +3534,7 @@
     <row r="78" spans="1:9" customHeight="0">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:26</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
@@ -3544,12 +3559,12 @@
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971411' for the user with id '209842' for the grade item with id '712649'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '209842'.</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -3561,7 +3576,7 @@
     <row r="79" spans="1:9" customHeight="0">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>19/09/26, 05:44:20</t>
+          <t>19/09/26, 05:44:26</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
@@ -3586,12 +3601,12 @@
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971410' for the user with id '209842' for the grade item with id '666279'.</t>
+          <t>The user with id '0' enrolled the user with id '209842' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -3628,12 +3643,12 @@
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t>Оценка удалена</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971409' for the user with id '209842' for the grade item with id '524410'.</t>
+          <t>The user with id '0' unenrolled the user with id '209842' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -3675,7 +3690,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971408' for the user with id '209842' for the grade item with id '212337'.</t>
+          <t>The user with id '0' deleted the grade with id '61971411' for the user with id '209842' for the grade item with id '712649'.</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -3717,7 +3732,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789133' for the user with id '209842' for the grade item with id '202565'.</t>
+          <t>The user with id '0' deleted the grade with id '61971410' for the user with id '209842' for the grade item with id '666279'.</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -3759,7 +3774,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789131' for the user with id '209842' for the grade item with id '202489'.</t>
+          <t>The user with id '0' deleted the grade with id '61971409' for the user with id '209842' for the grade item with id '524410'.</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -3801,7 +3816,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971407' for the user with id '209842' for the grade item with id '193468'.</t>
+          <t>The user with id '0' deleted the grade with id '61971408' for the user with id '209842' for the grade item with id '212337'.</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -3843,7 +3858,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971406' for the user with id '209842' for the grade item with id '162883'.</t>
+          <t>The user with id '0' deleted the grade with id '62789133' for the user with id '209842' for the grade item with id '202565'.</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -3885,7 +3900,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971405' for the user with id '209842' for the grade item with id '162882'.</t>
+          <t>The user with id '0' deleted the grade with id '62789131' for the user with id '209842' for the grade item with id '202489'.</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -3927,7 +3942,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '62789132' for the user with id '209842' for the grade item with id '162872'.</t>
+          <t>The user with id '0' deleted the grade with id '61971407' for the user with id '209842' for the grade item with id '193468'.</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -3969,7 +3984,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971404' for the user with id '209842' for the grade item with id '13852'.</t>
+          <t>The user with id '0' deleted the grade with id '61971406' for the user with id '209842' for the grade item with id '162883'.</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -4011,7 +4026,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971403' for the user with id '209842' for the grade item with id '13850'.</t>
+          <t>The user with id '0' deleted the grade with id '61971405' for the user with id '209842' for the grade item with id '162882'.</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -4053,7 +4068,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971402' for the user with id '209842' for the grade item with id '13847'.</t>
+          <t>The user with id '0' deleted the grade with id '62789132' for the user with id '209842' for the grade item with id '162872'.</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -4095,7 +4110,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971401' for the user with id '209842' for the grade item with id '13845'.</t>
+          <t>The user with id '0' deleted the grade with id '61971404' for the user with id '209842' for the grade item with id '13852'.</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -4137,7 +4152,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971400' for the user with id '209842' for the grade item with id '13842'.</t>
+          <t>The user with id '0' deleted the grade with id '61971403' for the user with id '209842' for the grade item with id '13850'.</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -4179,7 +4194,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971399' for the user with id '209842' for the grade item with id '13839'.</t>
+          <t>The user with id '0' deleted the grade with id '61971402' for the user with id '209842' for the grade item with id '13847'.</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -4221,7 +4236,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971398' for the user with id '209842' for the grade item with id '13836'.</t>
+          <t>The user with id '0' deleted the grade with id '61971401' for the user with id '209842' for the grade item with id '13845'.</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -4263,7 +4278,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971397' for the user with id '209842' for the grade item with id '13834'.</t>
+          <t>The user with id '0' deleted the grade with id '61971400' for the user with id '209842' for the grade item with id '13842'.</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -4305,7 +4320,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971396' for the user with id '209842' for the grade item with id '13830'.</t>
+          <t>The user with id '0' deleted the grade with id '61971399' for the user with id '209842' for the grade item with id '13839'.</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -4347,7 +4362,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971395' for the user with id '209842' for the grade item with id '13827'.</t>
+          <t>The user with id '0' deleted the grade with id '61971398' for the user with id '209842' for the grade item with id '13836'.</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -4389,7 +4404,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971393' for the user with id '209842' for the grade item with id '13823'.</t>
+          <t>The user with id '0' deleted the grade with id '61971397' for the user with id '209842' for the grade item with id '13834'.</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -4431,7 +4446,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' deleted the grade with id '61971394' for the user with id '209842' for the grade item with id '13821'.</t>
+          <t>The user with id '0' deleted the grade with id '61971396' for the user with id '209842' for the grade item with id '13830'.</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -4468,12 +4483,12 @@
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '209842'.</t>
+          <t>The user with id '0' deleted the grade with id '61971395' for the user with id '209842' for the grade item with id '13827'.</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -4510,12 +4525,12 @@
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '209842' from the group with id '107484'.</t>
+          <t>The user with id '0' deleted the grade with id '61971393' for the user with id '209842' for the grade item with id '13823'.</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -4527,148 +4542,133 @@
     <row r="102" spans="1:9" customHeight="0">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:46</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 1</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Оценка удалена</t>
         </is>
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '24773'.</t>
+          <t>The user with id '0' deleted the grade with id '61971394' for the user with id '209842' for the grade item with id '13821'.</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I102" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:9" customHeight="0">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:40</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 15</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '601904'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '209842'.</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I103" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:9" customHeight="0">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:30</t>
+          <t>19/09/26, 05:44:20</t>
         </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>Юркевич Илья Александрович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Емельянов Владимир Александрович</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 5</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the 'quiz' activity with course module id '440558'.</t>
+          <t>The user with id '0' removed the user with id '209842' from the group with id '107484'.</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I104" s="0" t="inlineStr">
-        <is>
-          <t>5.253.147.12</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:9" customHeight="0">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:33:26</t>
+          <t>17/09/26, 20:33:46</t>
         </is>
       </c>
       <c r="B105" s="0" t="inlineStr">
@@ -4683,22 +4683,22 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 1</t>
         </is>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F105" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '24773'.</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <row r="106" spans="1:9" customHeight="0">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 20:21:20</t>
+          <t>17/09/26, 20:33:40</t>
         </is>
       </c>
       <c r="B106" s="0" t="inlineStr">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 15</t>
         </is>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F106" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>The user with id '197464' viewed the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '601904'.</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -4762,12 +4762,12 @@
     <row r="107" spans="1:9" customHeight="0">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:13</t>
+          <t>17/09/26, 20:33:30</t>
         </is>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум</t>
+          <t>Тест: Задачи к лекции 5</t>
         </is>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F107" s="0" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the 'forum' activity with course module id '24770'.</t>
+          <t>The user with id '197464' viewed the 'quiz' activity with course module id '440558'.</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -4802,19 +4802,19 @@
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
-          <t>66.90.91.206</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:9" customHeight="0">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:07</t>
+          <t>17/09/26, 20:33:26</t>
         </is>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>Форум: Форум группы КИ 21-05б</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
-          <t>Форум</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F108" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the 'forum' activity with course module id '1343322'.</t>
+          <t>The user with id '197464' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -4849,19 +4849,19 @@
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
-          <t>66.90.91.206</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:9" customHeight="0">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>17/09/26, 00:35:04</t>
+          <t>17/09/26, 20:21:20</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>Юркевич Илья Александрович</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222427' viewed the course with id '1182'.</t>
+          <t>The user with id '197464' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -4896,108 +4896,118 @@
       </c>
       <c r="I109" s="0" t="inlineStr">
         <is>
-          <t>66.90.91.206</t>
+          <t>5.253.147.12</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:9" customHeight="0">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>17/09/26, 00:35:13</t>
         </is>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум</t>
         </is>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F110" s="0" t="inlineStr">
         <is>
-          <t>Член группы добавлен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' added the user with id '176234' to the group with id '107484'.</t>
+          <t>The user with id '222427' viewed the 'forum' activity with course module id '24770'.</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:9" customHeight="0">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>17/09/26, 00:35:07</t>
         </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Форум: Форум группы КИ 21-05б</t>
         </is>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Форум</t>
         </is>
       </c>
       <c r="F111" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' assigned the role with id '5' to the user with id '176234'.</t>
+          <t>The user with id '222427' viewed the 'forum' activity with course module id '1343322'.</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:9" customHeight="0">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 15:59:05</t>
+          <t>17/09/26, 00:35:04</t>
         </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>Василевская Дарья Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -5012,34 +5022,39 @@
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' enrolled the user with id '176234' using the enrolment method 'cohort' in the course with id '1182'.</t>
+          <t>The user with id '222427' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>66.90.91.206</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:9" customHeight="0">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 07:24:42</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -5054,86 +5069,76 @@
       </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Член группы добавлен</t>
         </is>
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' added the user with id '176234' to the group with id '107484'.</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I113" s="0" t="inlineStr">
-        <is>
-          <t>176.59.134.231</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:9" customHeight="0">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 01:47:10</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>Файл: Вопросы к экзамену КИ23-03, КИ23-04, КИ23-05</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F114" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the 'resource' activity with course module id '548778'.</t>
+          <t>The user with id '0' assigned the role with id '5' to the user with id '176234'.</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I114" s="0" t="inlineStr">
-        <is>
-          <t>176.116.166.86</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:9" customHeight="0">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>16/09/26, 01:43:34</t>
+          <t>16/09/26, 15:59:05</t>
         </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Василевская Дарья Александровна</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -5148,39 +5153,34 @@
       </c>
       <c r="F115" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '0' enrolled the user with id '176234' using the enrolment method 'cohort' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I115" s="0" t="inlineStr">
-        <is>
-          <t>176.116.166.86</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:9" customHeight="0">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:27:38</t>
+          <t>16/09/26, 07:24:42</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>Дульский Кирилл Геннадьевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="F116" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the profile for the user with id '222427' in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -5210,44 +5210,44 @@
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.59.134.231</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:9" customHeight="0">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:35</t>
+          <t>16/09/26, 01:47:10</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>Тимошенко Лев Евгеньевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Вопросы к экзамену КИ23-03, КИ23-04, КИ23-05</t>
         </is>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F117" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the profile for the user with id '222375' in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the 'resource' activity with course module id '548778'.</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -5257,19 +5257,19 @@
       </c>
       <c r="I117" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.116.166.86</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:9" customHeight="0">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:16</t>
+          <t>16/09/26, 01:43:34</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="F118" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -5304,14 +5304,14 @@
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>176.116.166.86</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:9" customHeight="0">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 14:26:10</t>
+          <t>14/09/26, 14:27:38</t>
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Дульский Кирилл Геннадьевич</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="F119" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the profile for the user with id '222427' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -5358,19 +5358,19 @@
     <row r="120" spans="1:9" customHeight="0">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>14/09/26, 11:39:31</t>
+          <t>14/09/26, 14:26:35</t>
         </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
+          <t>Федотова Ирина Михайловна</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
           <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
-      <c r="C120" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="D120" s="0" t="inlineStr">
         <is>
           <t>Курс: Математический анализ (Часть 2)</t>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="F120" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222375' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the profile for the user with id '222375' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -5398,19 +5398,19 @@
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>176.59.145.192</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:9" customHeight="0">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>12/09/26, 16:36:10</t>
+          <t>14/09/26, 14:26:16</t>
         </is>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>Моисеев Никита Андреевич</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="F121" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222376' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -5445,19 +5445,19 @@
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.144</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:9" customHeight="0">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t>11/09/26, 20:05:31</t>
+          <t>14/09/26, 14:26:10</t>
         </is>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>Рагозина Виктория Викторовна</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198852' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -5492,14 +5492,14 @@
       </c>
       <c r="I122" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.220</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:9" customHeight="0">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>11/09/26, 16:10:19</t>
+          <t>14/09/26, 11:39:31</t>
         </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
@@ -5539,24 +5539,24 @@
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>176.59.133.133</t>
+          <t>176.59.145.192</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:9" customHeight="0">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>12/09/26, 16:36:10</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Моисеев Никита Андреевич</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -5571,34 +5571,39 @@
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unenrolled the user with id '217794' using the enrolment method 'cohort' from the course with id '1182'.</t>
+          <t>The user with id '222376' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>188.0.28.144</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:9" customHeight="0">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>11/09/26, 20:05:31</t>
         </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Рагозина Виктория Викторовна</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -5613,34 +5618,39 @@
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' removed the user with id '217794' from the group with id '119772'.</t>
+          <t>The user with id '198852' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>188.0.28.220</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:9" customHeight="0">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>10/09/26, 05:49:04</t>
+          <t>11/09/26, 16:10:19</t>
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Тимошенко Лев Евгеньевич</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>Баканова Анастасия Валерьевна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -5655,81 +5665,81 @@
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' unassigned the role with id '5' from the user with id '217794'.</t>
+          <t>The user with id '222375' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>176.59.133.133</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:9" customHeight="0">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:41:03</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>Файл: Описание режима обучения</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the 'resource' activity with course module id '2056918'.</t>
+          <t>The user with id '0' unenrolled the user with id '217794' using the enrolment method 'cohort' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I127" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:9" customHeight="0">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:58</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -5744,76 +5754,66 @@
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the course with id '1182'.</t>
+          <t>The user with id '0' removed the user with id '217794' from the group with id '119772'.</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I128" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:9" customHeight="0">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:50</t>
+          <t>10/09/26, 05:49:04</t>
         </is>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>Федорова Валерия Игоревна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Баканова Анастасия Валерьевна</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
-          <t>Отчет по тесту просмотрен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
+          <t>The user with id '0' unassigned the role with id '5' from the user with id '217794'.</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="I129" s="0" t="inlineStr">
-        <is>
-          <t>10.128.134.198</t>
+          <t>cli</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:9" customHeight="0">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:39</t>
+          <t>9/09/26, 09:41:03</t>
         </is>
       </c>
       <c r="B130" s="0" t="inlineStr">
@@ -5828,22 +5828,22 @@
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Файл: Описание режима обучения</t>
         </is>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t>Отчет по тесту просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
+          <t>The user with id '115989' viewed the 'resource' activity with course module id '2056918'.</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -5860,7 +5860,7 @@
     <row r="131" spans="1:9" customHeight="0">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t>9/09/26, 09:40:25</t>
+          <t>9/09/26, 09:40:58</t>
         </is>
       </c>
       <c r="B131" s="0" t="inlineStr">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>The user with id '115989' viewed the 'quiz' activity with course module id '24836'.</t>
+          <t>The user with id '115989' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -5907,12 +5907,12 @@
     <row r="132" spans="1:9" customHeight="0">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:48</t>
+          <t>9/09/26, 09:40:50</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Отчет по тесту просмотрен</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -5947,44 +5947,44 @@
       </c>
       <c r="I132" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:9" customHeight="0">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:43</t>
+          <t>9/09/26, 09:40:39</t>
         </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F133" s="0" t="inlineStr">
         <is>
-          <t>Пользователь отчислен из курса</t>
+          <t>Отчет по тесту просмотрен</t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' unenrolled the user with id '237748' using the enrolment method 'manual' from the course with id '1182'.</t>
+          <t>The user with id '115989' viewed the report 'overview' for the quiz with course module id '24836'.</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -5994,44 +5994,44 @@
       </c>
       <c r="I133" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:9" customHeight="0">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:43</t>
+          <t>9/09/26, 09:40:25</t>
         </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Федорова Валерия Игоревна</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>Кушнер Тимур Васильевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 14</t>
         </is>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t>Назначение роли снято</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' unassigned the role with id '5' from the user with id '237748'.</t>
+          <t>The user with id '115989' viewed the 'quiz' activity with course module id '24836'.</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="I134" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>10.128.134.198</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:9" customHeight="0">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:06:28</t>
+          <t>7/09/26, 12:06:48</t>
         </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="F135" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -6095,7 +6095,7 @@
     <row r="136" spans="1:9" customHeight="0">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:05:46</t>
+          <t>7/09/26, 12:06:43</t>
         </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
-          <t>Член группы удален</t>
+          <t>Пользователь отчислен из курса</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' removed the user with id '237748' from the group with id '118487'.</t>
+          <t>The user with id '20261' unenrolled the user with id '237748' using the enrolment method 'manual' from the course with id '1182'.</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -6142,7 +6142,7 @@
     <row r="137" spans="1:9" customHeight="0">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:05:01</t>
+          <t>7/09/26, 12:06:43</t>
         </is>
       </c>
       <c r="B137" s="0" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
-          <t>Член группы добавлен</t>
+          <t>Назначение роли снято</t>
         </is>
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' added the user with id '237748' to the group with id '118487'.</t>
+          <t>The user with id '20261' unassigned the role with id '5' from the user with id '237748'.</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -6189,7 +6189,7 @@
     <row r="138" spans="1:9" customHeight="0">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:57</t>
+          <t>7/09/26, 12:06:28</t>
         </is>
       </c>
       <c r="B138" s="0" t="inlineStr">
@@ -6236,7 +6236,7 @@
     <row r="139" spans="1:9" customHeight="0">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:50</t>
+          <t>7/09/26, 12:05:46</t>
         </is>
       </c>
       <c r="B139" s="0" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
-          <t>Роль назначена</t>
+          <t>Член группы удален</t>
         </is>
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' assigned the role with id '5' to the user with id '237748'.</t>
+          <t>The user with id '20261' removed the user with id '237748' from the group with id '118487'.</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -6283,7 +6283,7 @@
     <row r="140" spans="1:9" customHeight="0">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:03:50</t>
+          <t>7/09/26, 12:05:01</t>
         </is>
       </c>
       <c r="B140" s="0" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="F140" s="0" t="inlineStr">
         <is>
-          <t>Пользователь зачислен на курс</t>
+          <t>Член группы добавлен</t>
         </is>
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' enrolled the user with id '237748' using the enrolment method 'manual' in the course with id '1182'.</t>
+          <t>The user with id '20261' added the user with id '237748' to the group with id '118487'.</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -6330,7 +6330,7 @@
     <row r="141" spans="1:9" customHeight="0">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:02:43</t>
+          <t>7/09/26, 12:03:57</t>
         </is>
       </c>
       <c r="B141" s="0" t="inlineStr">
@@ -6377,7 +6377,7 @@
     <row r="142" spans="1:9" customHeight="0">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 12:02:39</t>
+          <t>7/09/26, 12:03:50</t>
         </is>
       </c>
       <c r="B142" s="0" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="F142" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Роль назначена</t>
         </is>
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' assigned the role with id '5' to the user with id '237748'.</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -6424,17 +6424,17 @@
     <row r="143" spans="1:9" customHeight="0">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t>7/09/26, 11:42:02</t>
+          <t>7/09/26, 12:03:50</t>
         </is>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>Лаушкин Григорий Вадимович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Кушнер Тимур Васильевич</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="F143" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Пользователь зачислен на курс</t>
         </is>
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>The user with id '207594' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' enrolled the user with id '237748' using the enrolment method 'manual' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -6464,14 +6464,14 @@
       </c>
       <c r="I143" s="0" t="inlineStr">
         <is>
-          <t>10.30.102.26</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:9" customHeight="0">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t>3/09/26, 13:49:56</t>
+          <t>7/09/26, 12:02:43</t>
         </is>
       </c>
       <c r="B144" s="0" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="F144" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the section with id '12702'.</t>
+          <t>The user with id '20261' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="145" spans="1:9" customHeight="0">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t>3/09/26, 13:49:45</t>
+          <t>7/09/26, 12:02:39</t>
         </is>
       </c>
       <c r="B145" s="0" t="inlineStr">
@@ -6565,12 +6565,12 @@
     <row r="146" spans="1:9" customHeight="0">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 18:03:03</t>
+          <t>7/09/26, 11:42:02</t>
         </is>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>Попова Виктория Максимовна</t>
+          <t>Лаушкин Григорий Вадимович</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -6580,22 +6580,22 @@
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 5</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F146" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221894' viewed the 'quiz' activity with course module id '440558'.</t>
+          <t>The user with id '207594' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -6605,19 +6605,19 @@
       </c>
       <c r="I146" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.152</t>
+          <t>10.30.102.26</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:9" customHeight="0">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 18:02:48</t>
+          <t>3/09/26, 13:49:56</t>
         </is>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>Попова Виктория Максимовна</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="F147" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Раздел просмотрен</t>
         </is>
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221894' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the section with id '12702'.</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -6652,19 +6652,19 @@
       </c>
       <c r="I147" s="0" t="inlineStr">
         <is>
-          <t>188.0.28.152</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:9" customHeight="0">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t>2/09/26, 03:09:22</t>
+          <t>3/09/26, 13:49:45</t>
         </is>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>Ярусов Семён Александрович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222505' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -6699,44 +6699,44 @@
       </c>
       <c r="I148" s="0" t="inlineStr">
         <is>
-          <t>10.132.0.234</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:9" customHeight="0">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t>31/08/26, 17:07:41</t>
+          <t>2/09/26, 18:03:03</t>
         </is>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>Попова Виктория Максимовна</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 5</t>
         </is>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
-          <t>Отчет по пользователю</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
-          <t>Отчет «Отчет по пользователю» просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>The user with id '217787' viewed the user report in the gradebook.</t>
+          <t>The user with id '221894' viewed the 'quiz' activity with course module id '440558'.</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -6746,19 +6746,19 @@
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>
-          <t>89.113.136.51</t>
+          <t>188.0.28.152</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:9" customHeight="0">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t>31/08/26, 17:07:36</t>
+          <t>2/09/26, 18:02:48</t>
         </is>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>Айдеян Артак Акобович</t>
+          <t>Попова Виктория Максимовна</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>The user with id '217787' viewed the course with id '1182'.</t>
+          <t>The user with id '221894' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -6793,19 +6793,19 @@
       </c>
       <c r="I150" s="0" t="inlineStr">
         <is>
-          <t>89.113.136.51</t>
+          <t>188.0.28.152</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:9" customHeight="0">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 18:46:50</t>
+          <t>2/09/26, 03:09:22</t>
         </is>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>Николаев Виктор Анатольевич</t>
+          <t>Ярусов Семён Александрович</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>The user with id '221862' viewed the course with id '1182'.</t>
+          <t>The user with id '222505' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -6840,44 +6840,44 @@
       </c>
       <c r="I151" s="0" t="inlineStr">
         <is>
-          <t>176.59.130.167</t>
+          <t>10.132.0.234</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:9" customHeight="0">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:06:13</t>
+          <t>31/08/26, 17:07:41</t>
         </is>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Отчет по пользователю</t>
         </is>
       </c>
       <c r="F152" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Отчет «Отчет по пользователю» просмотрен</t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the 'resource' activity with course module id '24771'.</t>
+          <t>The user with id '217787' viewed the user report in the gradebook.</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -6887,19 +6887,19 @@
       </c>
       <c r="I152" s="0" t="inlineStr">
         <is>
-          <t>10.30.119.34</t>
+          <t>89.113.136.51</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:9" customHeight="0">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:05:42</t>
+          <t>31/08/26, 17:07:36</t>
         </is>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>Айдеян Артак Акобович</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the course with id '1182'.</t>
+          <t>The user with id '217787' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -6934,24 +6934,24 @@
       </c>
       <c r="I153" s="0" t="inlineStr">
         <is>
-          <t>10.30.119.34</t>
+          <t>89.113.136.51</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:9" customHeight="0">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t>30/08/26, 01:05:39</t>
+          <t>30/08/26, 18:46:50</t>
         </is>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>Шкредов Сергей Александрович</t>
+          <t>Николаев Виктор Анатольевич</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>Тисецкая Анастасия Александровна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F154" s="0" t="inlineStr">
         <is>
-          <t>Профиль пользователя просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>The user with id '198420' viewed the profile for the user with id '196462' in the course with id '1182'.</t>
+          <t>The user with id '221862' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -6981,44 +6981,44 @@
       </c>
       <c r="I154" s="0" t="inlineStr">
         <is>
-          <t>10.30.119.34</t>
+          <t>176.59.130.167</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:9" customHeight="0">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:29</t>
+          <t>30/08/26, 01:06:13</t>
         </is>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 6</t>
+          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
         </is>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F155" s="0" t="inlineStr">
         <is>
-          <t>Завершенная попытка теста просмотрена</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' has reviewed quiz attempt with id '9161794' by user with id '218896' for the quiz with course module id '24797'.</t>
+          <t>The user with id '198420' viewed the 'resource' activity with course module id '24771'.</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -7028,19 +7028,19 @@
       </c>
       <c r="I155" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:9" customHeight="0">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:23</t>
+          <t>30/08/26, 01:05:42</t>
         </is>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -7050,22 +7050,22 @@
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 6</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F156" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the 'quiz' activity with course module id '24797'.</t>
+          <t>The user with id '198420' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -7075,24 +7075,24 @@
       </c>
       <c r="I156" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:9" customHeight="0">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:48:11</t>
+          <t>30/08/26, 01:05:39</t>
         </is>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Шкредов Сергей Александрович</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>Иванов Данил Андреевич</t>
+          <t>Тисецкая Анастасия Александровна</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="F157" s="0" t="inlineStr">
         <is>
-          <t>Отчет по участнику курса просмотрен</t>
+          <t>Профиль пользователя просмотрен</t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the user report for the course with id '1182' for user with id '218896'.</t>
+          <t>The user with id '198420' viewed the profile for the user with id '196462' in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -7122,14 +7122,14 @@
       </c>
       <c r="I157" s="0" t="inlineStr">
         <is>
-          <t>178.34.136.28</t>
+          <t>10.30.119.34</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:9" customHeight="0">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t>29/08/26, 21:47:40</t>
+          <t>29/08/26, 21:48:29</t>
         </is>
       </c>
       <c r="B158" s="0" t="inlineStr">
@@ -7139,27 +7139,27 @@
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 6</t>
         </is>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F158" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Завершенная попытка теста просмотрена</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218896' viewed the course with id '1182'.</t>
+          <t>The user with id '218896' has reviewed quiz attempt with id '9161794' by user with id '218896' for the quiz with course module id '24797'.</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -7176,12 +7176,12 @@
     <row r="159" spans="1:9" customHeight="0">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t>28/08/26, 14:05:02</t>
+          <t>29/08/26, 21:48:23</t>
         </is>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>Шишигин Никита Геннадьевич</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -7191,22 +7191,22 @@
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Тест: Задачи к лекции 6</t>
         </is>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F159" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>The user with id '220735' viewed the course with id '1182'.</t>
+          <t>The user with id '218896' viewed the 'quiz' activity with course module id '24797'.</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="I159" s="0" t="inlineStr">
         <is>
-          <t>91.132.20.254</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:9" customHeight="0">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t>26/08/26, 20:49:54</t>
+          <t>29/08/26, 21:48:11</t>
         </is>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="F160" s="0" t="inlineStr">
         <is>
-          <t>Просмотрено описание курса</t>
+          <t>Отчет по участнику курса просмотрен</t>
         </is>
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
+          <t>The user with id '218896' viewed the user report for the course with id '1182' for user with id '218896'.</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -7263,19 +7263,19 @@
       </c>
       <c r="I160" s="0" t="inlineStr">
         <is>
-          <t>5.255.231.81</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:9" customHeight="0">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t>20/08/26, 23:30:20</t>
+          <t>29/08/26, 21:47:40</t>
         </is>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>Ооржак Анчы Вячеславович</t>
+          <t>Иванов Данил Андреевич</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="F161" s="0" t="inlineStr">
         <is>
-          <t>Список пользователей просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222788' viewed the list of users in the course with id '1182'.</t>
+          <t>The user with id '218896' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -7310,19 +7310,19 @@
       </c>
       <c r="I161" s="0" t="inlineStr">
         <is>
-          <t>185.193.199.22</t>
+          <t>178.34.136.28</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:9" customHeight="0">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t>20/08/26, 23:30:17</t>
+          <t>28/08/26, 14:05:02</t>
         </is>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>Ооржак Анчы Вячеславович</t>
+          <t>Шишигин Никита Геннадьевич</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222788' viewed the course with id '1182'.</t>
+          <t>The user with id '220735' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -7357,19 +7357,19 @@
       </c>
       <c r="I162" s="0" t="inlineStr">
         <is>
-          <t>185.193.199.22</t>
+          <t>91.132.20.254</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:9" customHeight="0">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:26</t>
+          <t>26/08/26, 20:49:54</t>
         </is>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="F163" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Просмотрено описание курса</t>
         </is>
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '0' viewed the course information for the course with id '1182'.</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -7404,19 +7404,19 @@
       </c>
       <c r="I163" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>5.255.231.81</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:9" customHeight="0">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:23</t>
+          <t>20/08/26, 23:30:20</t>
         </is>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Ооржак Анчы Вячеславович</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="F164" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Список пользователей просмотрен</t>
         </is>
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '222788' viewed the list of users in the course with id '1182'.</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -7451,19 +7451,19 @@
       </c>
       <c r="I164" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>185.193.199.22</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:9" customHeight="0">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:27:22</t>
+          <t>20/08/26, 23:30:17</t>
         </is>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>Федотова Ирина Михайловна</t>
+          <t>Ооржак Анчы Вячеславович</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="F165" s="0" t="inlineStr">
         <is>
-          <t>Курс обновлен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' updated the course with id '1182'.</t>
+          <t>The user with id '222788' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -7498,14 +7498,14 @@
       </c>
       <c r="I165" s="0" t="inlineStr">
         <is>
-          <t>10.3.73.136</t>
+          <t>185.193.199.22</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:9" customHeight="0">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:40</t>
+          <t>18/08/26, 12:27:26</t>
         </is>
       </c>
       <c r="B166" s="0" t="inlineStr">
@@ -7552,7 +7552,7 @@
     <row r="167" spans="1:9" customHeight="0">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:20</t>
+          <t>18/08/26, 12:27:23</t>
         </is>
       </c>
       <c r="B167" s="0" t="inlineStr">
@@ -7599,7 +7599,7 @@
     <row r="168" spans="1:9" customHeight="0">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:12</t>
+          <t>18/08/26, 12:27:22</t>
         </is>
       </c>
       <c r="B168" s="0" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="F168" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Курс обновлен</t>
         </is>
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' updated the course with id '1182'.</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -7646,7 +7646,7 @@
     <row r="169" spans="1:9" customHeight="0">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:26:12</t>
+          <t>18/08/26, 12:26:40</t>
         </is>
       </c>
       <c r="B169" s="0" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="F169" s="0" t="inlineStr">
         <is>
-          <t>Курс обновлен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' updated the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -7693,7 +7693,7 @@
     <row r="170" spans="1:9" customHeight="0">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:55</t>
+          <t>18/08/26, 12:26:20</t>
         </is>
       </c>
       <c r="B170" s="0" t="inlineStr">
@@ -7740,7 +7740,7 @@
     <row r="171" spans="1:9" customHeight="0">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:17</t>
+          <t>18/08/26, 12:26:12</t>
         </is>
       </c>
       <c r="B171" s="0" t="inlineStr">
@@ -7787,7 +7787,7 @@
     <row r="172" spans="1:9" customHeight="0">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:21:03</t>
+          <t>18/08/26, 12:26:12</t>
         </is>
       </c>
       <c r="B172" s="0" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="F172" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Курс обновлен</t>
         </is>
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>The user with id '20261' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' updated the course with id '1182'.</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -7834,7 +7834,7 @@
     <row r="173" spans="1:9" customHeight="0">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t>18/08/26, 12:20:38</t>
+          <t>18/08/26, 12:21:55</t>
         </is>
       </c>
       <c r="B173" s="0" t="inlineStr">
@@ -7881,12 +7881,12 @@
     <row r="174" spans="1:9" customHeight="0">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t>17/08/26, 13:54:23</t>
+          <t>18/08/26, 12:21:17</t>
         </is>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>Гудин Степан Денисович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -7896,22 +7896,22 @@
       </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 2</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F174" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222257' viewed the 'quiz' activity with course module id '24778'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -7921,19 +7921,19 @@
       </c>
       <c r="I174" s="0" t="inlineStr">
         <is>
-          <t>10.28.71.178</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:9" customHeight="0">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t>17/08/26, 13:54:13</t>
+          <t>18/08/26, 12:21:03</t>
         </is>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>Гудин Степан Денисович</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222257' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -7968,19 +7968,19 @@
       </c>
       <c r="I175" s="0" t="inlineStr">
         <is>
-          <t>10.28.71.178</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:9" customHeight="0">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 19:11:54</t>
+          <t>18/08/26, 12:20:38</t>
         </is>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Федотова Ирина Михайловна</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '20261' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -8015,19 +8015,19 @@
       </c>
       <c r="I176" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>10.3.73.136</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:9" customHeight="0">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 17:28:04</t>
+          <t>17/08/26, 13:54:23</t>
         </is>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Гудин Степан Денисович</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="D177" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
+          <t>Тест: Задачи к лекции 2</t>
         </is>
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="F177" s="0" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the 'resource' activity with course module id '24771'.</t>
+          <t>The user with id '222257' viewed the 'quiz' activity with course module id '24778'.</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -8062,19 +8062,19 @@
       </c>
       <c r="I177" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>10.28.71.178</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:9" customHeight="0">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 17:23:59</t>
+          <t>17/08/26, 13:54:13</t>
         </is>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>Яцинович Антон Николаевич</t>
+          <t>Гудин Степан Денисович</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>The user with id '222925' viewed the course with id '1182'.</t>
+          <t>The user with id '222257' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -8109,19 +8109,19 @@
       </c>
       <c r="I178" s="0" t="inlineStr">
         <is>
-          <t>176.49.89.56</t>
+          <t>10.28.71.178</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:9" customHeight="0">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:25</t>
+          <t>16/08/26, 19:11:54</t>
         </is>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="F179" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '171426'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -8156,19 +8156,19 @@
       </c>
       <c r="I179" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>176.49.89.56</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:9" customHeight="0">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:21</t>
+          <t>16/08/26, 17:28:04</t>
         </is>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 8. Формула Грина. Независимость криволинейного интеграла 2-го рода от пути интегрирования</t>
+          <t>Файл: Лекция 1. Понятие ФНП. Предел, непрерывность. Частные производные</t>
         </is>
       </c>
       <c r="E180" s="0" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '440562'.</t>
+          <t>The user with id '222925' viewed the 'resource' activity with course module id '24771'.</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -8203,19 +8203,19 @@
       </c>
       <c r="I180" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>176.49.89.56</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:9" customHeight="0">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:09</t>
+          <t>16/08/26, 17:23:59</t>
         </is>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>Марков Сергей Денисович</t>
+          <t>Яцинович Антон Николаевич</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="F181" s="0" t="inlineStr">
         <is>
-          <t>Раздел просмотрен</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12711'.</t>
+          <t>The user with id '222925' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -8250,14 +8250,14 @@
       </c>
       <c r="I181" s="0" t="inlineStr">
         <is>
-          <t>62.68.153.224</t>
+          <t>176.49.89.56</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:9" customHeight="0">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:05</t>
+          <t>16/08/26, 00:10:25</t>
         </is>
       </c>
       <c r="B182" s="0" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12714'.</t>
+          <t>The user with id '223842' viewed the section with id '171426'.</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -8304,7 +8304,7 @@
     <row r="183" spans="1:9" customHeight="0">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:10:01</t>
+          <t>16/08/26, 00:10:21</t>
         </is>
       </c>
       <c r="B183" s="0" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 16. Функциональные ряды. Основные понятия. Степенные ряды. Свойства степенных рядов. Разложение функции в степенные ряды. Ряд Тейлора. Ряд Маклорена</t>
+          <t>Файл: Лекция 8. Формула Грина. Независимость криволинейного интеграла 2-го рода от пути интегрирования</t>
         </is>
       </c>
       <c r="E183" s="0" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '440645'.</t>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '440562'.</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -8351,7 +8351,7 @@
     <row r="184" spans="1:9" customHeight="0">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:56</t>
+          <t>16/08/26, 00:10:09</t>
         </is>
       </c>
       <c r="B184" s="0" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the section with id '12706'.</t>
+          <t>The user with id '223842' viewed the section with id '12711'.</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -8398,7 +8398,7 @@
     <row r="185" spans="1:9" customHeight="0">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:47</t>
+          <t>16/08/26, 00:10:05</t>
         </is>
       </c>
       <c r="B185" s="0" t="inlineStr">
@@ -8413,22 +8413,22 @@
       </c>
       <c r="D185" s="0" t="inlineStr">
         <is>
-          <t>Файл: Лекция 2.  Дифференцируемость и полный дифференциал ФНП. Дифференциалы высших порядков. Производная сложной функции. Производная неявной функции. Производная по направлению. Градиент</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
-          <t>Файл</t>
+          <t>Система</t>
         </is>
       </c>
       <c r="F185" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса просмотрен</t>
+          <t>Раздел просмотрен</t>
         </is>
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the 'resource' activity with course module id '24776'.</t>
+          <t>The user with id '223842' viewed the section with id '12714'.</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -8445,7 +8445,7 @@
     <row r="186" spans="1:9" customHeight="0">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t>16/08/26, 00:09:40</t>
+          <t>16/08/26, 00:10:01</t>
         </is>
       </c>
       <c r="B186" s="0" t="inlineStr">
@@ -8460,22 +8460,22 @@
       </c>
       <c r="D186" s="0" t="inlineStr">
         <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
+          <t>Файл: Лекция 16. Функциональные ряды. Основные понятия. Степенные ряды. Свойства степенных рядов. Разложение функции в степенные ряды. Ряд Тейлора. Ряд Маклорена</t>
         </is>
       </c>
       <c r="E186" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F186" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>The user with id '223842' viewed the course with id '1182'.</t>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '440645'.</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -8492,12 +8492,12 @@
     <row r="187" spans="1:9" customHeight="0">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t>31/07/26, 13:15:41</t>
+          <t>16/08/26, 00:09:56</t>
         </is>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>Войченко Антон Дмитриевич</t>
+          <t>Марков Сергей Денисович</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="F187" s="0" t="inlineStr">
         <is>
-          <t>Курс просмотрен</t>
+          <t>Раздел просмотрен</t>
         </is>
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>The user with id '218660' viewed the course with id '1182'.</t>
+          <t>The user with id '223842' viewed the section with id '12706'.</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -8532,19 +8532,19 @@
       </c>
       <c r="I187" s="0" t="inlineStr">
         <is>
-          <t>193.8.74.6</t>
+          <t>62.68.153.224</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:9" customHeight="0">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t>16/07/26, 16:23:26</t>
+          <t>16/08/26, 00:09:47</t>
         </is>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>Администратор системы</t>
+          <t>Марков Сергей Денисович</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -8554,39 +8554,44 @@
       </c>
       <c r="D188" s="0" t="inlineStr">
         <is>
-          <t>Тест: Задачи к лекции 14</t>
+          <t>Файл: Лекция 2.  Дифференцируемость и полный дифференциал ФНП. Дифференциалы высших порядков. Производная сложной функции. Производная неявной функции. Производная по направлению. Градиент</t>
         </is>
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
-          <t>Система</t>
+          <t>Файл</t>
         </is>
       </c>
       <c r="F188" s="0" t="inlineStr">
         <is>
-          <t>Вопрос удален</t>
+          <t>Модуль курса просмотрен</t>
         </is>
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>The user with id '2' deleted the question with id '103599' from the category with the id '7395'.</t>
+          <t>The user with id '223842' viewed the 'resource' activity with course module id '24776'.</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I188" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:9" customHeight="0">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t>16/07/26, 16:23:26</t>
+          <t>16/08/26, 00:09:40</t>
         </is>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>Администратор системы</t>
+          <t>Марков Сергей Денисович</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -8596,7 +8601,7 @@
       </c>
       <c r="D189" s="0" t="inlineStr">
         <is>
-          <t>Банк вопросов: Математический анализ (Часть 2) - общий банк вопросов</t>
+          <t>Курс: Математический анализ (Часть 2)</t>
         </is>
       </c>
       <c r="E189" s="0" t="inlineStr">
@@ -8606,57 +8611,193 @@
       </c>
       <c r="F189" s="0" t="inlineStr">
         <is>
-          <t>Модуль курса создан</t>
+          <t>Курс просмотрен</t>
         </is>
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>The user with id '2' created the 'qbank' activity with course module id '2058071'.</t>
+          <t>The user with id '223842' viewed the course with id '1182'.</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I189" s="0" t="inlineStr">
+        <is>
+          <t>62.68.153.224</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:9" customHeight="0">
       <c r="A190" s="0" t="inlineStr">
         <is>
+          <t>31/07/26, 13:15:41</t>
+        </is>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>Войченко Антон Дмитриевич</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F190" s="0" t="inlineStr">
+        <is>
+          <t>Курс просмотрен</t>
+        </is>
+      </c>
+      <c r="G190" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '218660' viewed the course with id '1182'.</t>
+        </is>
+      </c>
+      <c r="H190" s="0" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="I190" s="0" t="inlineStr">
+        <is>
+          <t>193.8.74.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" spans="1:9" customHeight="0">
+      <c r="A191" s="0" t="inlineStr">
+        <is>
           <t>16/07/26, 16:23:26</t>
         </is>
       </c>
-      <c r="B190" s="0" t="inlineStr">
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>Администратор системы</t>
         </is>
       </c>
-      <c r="C190" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D190" s="0" t="inlineStr">
-        <is>
-          <t>Курс: Математический анализ (Часть 2)</t>
-        </is>
-      </c>
-      <c r="E190" s="0" t="inlineStr">
-        <is>
-          <t>Система</t>
-        </is>
-      </c>
-      <c r="F190" s="0" t="inlineStr">
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>Тест: Задачи к лекции 14</t>
+        </is>
+      </c>
+      <c r="E191" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F191" s="0" t="inlineStr">
         <is>
           <t>Вопрос удален</t>
         </is>
       </c>
-      <c r="G190" s="0" t="inlineStr">
+      <c r="G191" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '2' deleted the question with id '103599' from the category with the id '7395'.</t>
+        </is>
+      </c>
+      <c r="H191" s="0" t="inlineStr">
+        <is>
+          <t>cli</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" spans="1:9" customHeight="0">
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t>16/07/26, 16:23:26</t>
+        </is>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t>Администратор системы</t>
+        </is>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>Банк вопросов: Математический анализ (Часть 2) - общий банк вопросов</t>
+        </is>
+      </c>
+      <c r="E192" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F192" s="0" t="inlineStr">
+        <is>
+          <t>Модуль курса создан</t>
+        </is>
+      </c>
+      <c r="G192" s="0" t="inlineStr">
+        <is>
+          <t>The user with id '2' created the 'qbank' activity with course module id '2058071'.</t>
+        </is>
+      </c>
+      <c r="H192" s="0" t="inlineStr">
+        <is>
+          <t>cli</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" spans="1:9" customHeight="0">
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t>16/07/26, 16:23:26</t>
+        </is>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t>Администратор системы</t>
+        </is>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t>Курс: Математический анализ (Часть 2)</t>
+        </is>
+      </c>
+      <c r="E193" s="0" t="inlineStr">
+        <is>
+          <t>Система</t>
+        </is>
+      </c>
+      <c r="F193" s="0" t="inlineStr">
+        <is>
+          <t>Вопрос удален</t>
+        </is>
+      </c>
+      <c r="G193" s="0" t="inlineStr">
         <is>
           <t>The user with id '2' deleted the question with id '6639287' from the category with the id '405065'.</t>
         </is>
       </c>
-      <c r="H190" s="0" t="inlineStr">
+      <c r="H193" s="0" t="inlineStr">
         <is>
           <t>cli</t>
         </is>
